--- a/KatalonData/VLinkCCTestData.xlsx
+++ b/KatalonData/VLinkCCTestData.xlsx
@@ -1,28 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A97E742-F5E4-47E1-8936-0F55E9478DFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr documentId="13_ncr:1_{BC086086-A28B-4DB9-846E-AA23A341CF6D}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{8C2F89C9-A10B-4559-913F-0962936A94D9}"/>
+    <workbookView windowHeight="15675" windowWidth="28996" xWindow="-98" xr2:uid="{8C2F89C9-A10B-4559-913F-0962936A94D9}" yWindow="-98"/>
   </bookViews>
   <sheets>
-    <sheet name="CCSaleData" sheetId="1" r:id="rId1"/>
-    <sheet name="Trial" sheetId="4" r:id="rId2"/>
-    <sheet name="AuthAndCaptureData" sheetId="3" r:id="rId3"/>
+    <sheet name="CCSaleData" r:id="rId1" sheetId="1"/>
+    <sheet name="Trial" r:id="rId2" sheetId="4"/>
+    <sheet name="AuthAndCaptureData" r:id="rId3" sheetId="3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CCSaleData!$G$1:$G$175</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">CCSaleData!$G$1:$G$175</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8600" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8534" uniqueCount="387">
   <si>
     <t>Notes</t>
   </si>
@@ -613,9 +613,6 @@
     <t>pwd501</t>
   </si>
   <si>
-    <t>Thu Aug 14 17:33:12 EDT 2025</t>
-  </si>
-  <si>
     <t>Thu Aug 14 17:33:28 EDT 2025</t>
   </si>
   <si>
@@ -1124,12 +1121,91 @@
   </si>
   <si>
     <t>Req Fields Only FDMS Rapid Connect</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 11:52:57 EST 2026</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Sat Feb 14 11:55:06 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 11:57:31 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 11:59:53 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 12:02:17 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 12:04:40 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 12:06:59 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 12:09:23 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 12:11:47 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 12:14:10 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 12:16:33 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 12:18:56 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 12:21:20 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 12:23:43 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 12:26:06 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 12:28:30 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 12:30:53 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 12:33:17 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 12:35:40 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 12:38:03 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 12:40:27 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 12:42:50 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 12:45:13 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 12:47:45 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 12:50:03 EST 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1178,21 +1254,21 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
+    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0"/>
+    <xf applyBorder="1" borderId="1" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle builtinId="0" name="Normal" xfId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1209,10 +1285,10 @@
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -1247,7 +1323,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -1299,7 +1375,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -1410,21 +1486,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -1441,7 +1517,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -1493,76 +1569,76 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office 2013 - 2022 Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01D907F6-7637-41F5-9F0A-BDDAA86240AA}">
-  <dimension ref="A1:AX175"/>
-  <sheetFormatPr defaultColWidth="26.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01D907F6-7637-41F5-9F0A-BDDAA86240AA}">
+  <dimension ref="A1:AY175"/>
+  <sheetFormatPr defaultColWidth="26.73046875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.1796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="26.7265625" style="1" collapsed="1"/>
-    <col min="3" max="3" width="36" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="32" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="9.1796875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="4.7265625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="6.453125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="10" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="9.453125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="11.7265625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="8.81640625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="12" max="12" width="6.7265625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="13" max="13" width="13.7265625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="14" max="14" width="19.1796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="15" max="15" width="22.26953125" style="1" customWidth="1" collapsed="1"/>
-    <col min="16" max="16" width="8" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="17" max="17" width="9.26953125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="18" max="18" width="5.54296875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="19" max="19" width="6" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="20" max="20" width="9.81640625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="21" max="21" width="8.1796875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="22" max="22" width="24" style="1" customWidth="1" collapsed="1"/>
-    <col min="23" max="23" width="4.7265625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="24" max="24" width="8.81640625" style="1" customWidth="1" collapsed="1"/>
-    <col min="25" max="25" width="8.7265625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="26" max="26" width="9.26953125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="27" max="27" width="115.453125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="28" max="28" width="75.54296875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="29" max="29" width="40.54296875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="30" max="30" width="14.453125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="31" max="31" width="23.81640625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="32" max="32" width="13.54296875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="33" max="33" width="11.1796875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="34" max="34" width="18" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="35" max="35" width="7" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="36" max="36" width="14.7265625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="37" max="45" width="10.453125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="46" max="46" width="11.453125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="47" max="48" width="13.7265625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="49" max="49" width="12.54296875" style="1" customWidth="1" collapsed="1"/>
-    <col min="50" max="50" width="15" style="1" customWidth="1" collapsed="1"/>
-    <col min="51" max="51" width="14.453125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="52" max="52" width="9.1796875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="53" max="53" width="12" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="54" max="54" width="11.54296875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="55" max="55" width="15.26953125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="56" max="56" width="14.7265625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="57" max="57" width="15.7265625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="58" max="58" width="11.81640625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="59" max="59" width="18.26953125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="60" max="60" width="14.81640625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="61" max="62" width="15.81640625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="63" max="63" width="16.453125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="64" max="64" width="10" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="65" max="65" width="10.7265625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="66" max="16384" width="26.7265625" style="1" collapsed="1"/>
+    <col min="1" max="1" customWidth="true" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" style="1" width="26.73046875" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="36.0" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="32.0" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="9.19921875" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="4.73046875" collapsed="true"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="6.46484375" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.0" collapsed="true"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="9.46484375" collapsed="true"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="1" width="11.73046875" collapsed="true"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="8.796875" collapsed="true"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="6.73046875" collapsed="true"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="13.73046875" collapsed="true"/>
+    <col min="14" max="14" customWidth="true" style="1" width="19.19921875" collapsed="true"/>
+    <col min="15" max="15" customWidth="true" style="1" width="22.265625" collapsed="true"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" style="1" width="8.0" collapsed="true"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.265625" collapsed="true"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="5.53125" collapsed="true"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="6.0" collapsed="true"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="9.796875" collapsed="true"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="8.19921875" collapsed="true"/>
+    <col min="22" max="22" customWidth="true" style="1" width="24.0" collapsed="true"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="4.73046875" collapsed="true"/>
+    <col min="24" max="24" customWidth="true" style="1" width="8.796875" collapsed="true"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" style="1" width="8.73046875" collapsed="true"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" style="1" width="9.265625" collapsed="true"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="115.46484375" collapsed="true"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="75.53125" collapsed="true"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="40.53125" collapsed="true"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="14.46484375" collapsed="true"/>
+    <col min="31" max="31" bestFit="true" customWidth="true" style="1" width="23.796875" collapsed="true"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="13.53125" collapsed="true"/>
+    <col min="33" max="33" bestFit="true" customWidth="true" style="1" width="11.19921875" collapsed="true"/>
+    <col min="34" max="34" bestFit="true" customWidth="true" style="1" width="18.0" collapsed="true"/>
+    <col min="35" max="35" bestFit="true" customWidth="true" style="1" width="7.0" collapsed="true"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" style="1" width="14.73046875" collapsed="true"/>
+    <col min="37" max="45" bestFit="true" customWidth="true" style="1" width="10.46484375" collapsed="true"/>
+    <col min="46" max="46" bestFit="true" customWidth="true" style="1" width="11.46484375" collapsed="true"/>
+    <col min="47" max="48" bestFit="true" customWidth="true" style="1" width="13.73046875" collapsed="true"/>
+    <col min="49" max="49" customWidth="true" style="1" width="12.53125" collapsed="true"/>
+    <col min="50" max="50" customWidth="true" style="1" width="15.0" collapsed="true"/>
+    <col min="51" max="51" bestFit="true" customWidth="true" style="1" width="14.46484375" collapsed="true"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" style="1" width="9.19921875" collapsed="true"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" style="1" width="12.0" collapsed="true"/>
+    <col min="54" max="54" bestFit="true" customWidth="true" style="1" width="11.53125" collapsed="true"/>
+    <col min="55" max="55" bestFit="true" customWidth="true" style="1" width="15.265625" collapsed="true"/>
+    <col min="56" max="56" bestFit="true" customWidth="true" style="1" width="14.73046875" collapsed="true"/>
+    <col min="57" max="57" bestFit="true" customWidth="true" style="1" width="15.73046875" collapsed="true"/>
+    <col min="58" max="58" bestFit="true" customWidth="true" style="1" width="11.796875" collapsed="true"/>
+    <col min="59" max="59" bestFit="true" customWidth="true" style="1" width="18.265625" collapsed="true"/>
+    <col min="60" max="60" bestFit="true" customWidth="true" style="1" width="14.796875" collapsed="true"/>
+    <col min="61" max="62" bestFit="true" customWidth="true" style="1" width="15.796875" collapsed="true"/>
+    <col min="63" max="63" bestFit="true" customWidth="true" style="1" width="16.46484375" collapsed="true"/>
+    <col min="64" max="64" bestFit="true" customWidth="true" style="1" width="10.0" collapsed="true"/>
+    <col min="65" max="65" bestFit="true" customWidth="true" style="1" width="10.73046875" collapsed="true"/>
+    <col min="66" max="16384" style="1" width="26.73046875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" ht="29" x14ac:dyDescent="0.35">
+    <row ht="28.5" r="1" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>145</v>
       </c>
@@ -1714,12 +1790,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B2" t="s">
-        <v>191</v>
+        <v>363</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>153</v>
@@ -1778,8 +1854,8 @@
       <c r="W2" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X2" s="1" t="s">
-        <v>103</v>
+      <c r="X2" s="1">
+        <v>2028</v>
       </c>
       <c r="AD2" s="1" t="s">
         <v>104</v>
@@ -1834,12 +1910,12 @@
       </c>
       <c r="AX2" s="2"/>
     </row>
-    <row r="3" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B3" t="s">
-        <v>192</v>
+        <v>364</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>153</v>
@@ -1892,8 +1968,8 @@
       <c r="W3" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="X3" s="1" t="s">
-        <v>110</v>
+      <c r="X3" s="1">
+        <v>2028</v>
       </c>
       <c r="AD3" s="1" t="s">
         <v>104</v>
@@ -1901,12 +1977,12 @@
       <c r="AE3" s="2"/>
       <c r="AX3" s="2"/>
     </row>
-    <row r="4" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B4" t="s">
-        <v>193</v>
+        <v>365</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>153</v>
@@ -1959,8 +2035,8 @@
       <c r="W4" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="X4" s="1" t="s">
-        <v>110</v>
+      <c r="X4" s="1">
+        <v>2028</v>
       </c>
       <c r="AD4" s="1" t="s">
         <v>104</v>
@@ -1968,12 +2044,12 @@
       <c r="AE4" s="2"/>
       <c r="AX4" s="2"/>
     </row>
-    <row r="5" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B5" t="s">
-        <v>194</v>
+        <v>366</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>153</v>
@@ -2032,8 +2108,8 @@
       <c r="W5" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X5" s="1" t="s">
-        <v>103</v>
+      <c r="X5" s="1">
+        <v>2028</v>
       </c>
       <c r="AD5" s="1" t="s">
         <v>104</v>
@@ -2088,12 +2164,12 @@
       </c>
       <c r="AX5" s="2"/>
     </row>
-    <row r="6" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B6" t="s">
-        <v>195</v>
+        <v>367</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>153</v>
@@ -2146,8 +2222,8 @@
       <c r="W6" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="X6" s="1" t="s">
-        <v>110</v>
+      <c r="X6" s="1">
+        <v>2028</v>
       </c>
       <c r="AD6" s="1" t="s">
         <v>104</v>
@@ -2155,12 +2231,12 @@
       <c r="AE6" s="2"/>
       <c r="AX6" s="2"/>
     </row>
-    <row r="7" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B7" t="s">
-        <v>196</v>
+        <v>368</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>153</v>
@@ -2213,8 +2289,8 @@
       <c r="W7" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="X7" s="1" t="s">
-        <v>110</v>
+      <c r="X7" s="1">
+        <v>2028</v>
       </c>
       <c r="AD7" s="1" t="s">
         <v>104</v>
@@ -2222,12 +2298,12 @@
       <c r="AE7" s="2"/>
       <c r="AX7" s="2"/>
     </row>
-    <row r="8" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B8" t="s">
-        <v>197</v>
+        <v>369</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>153</v>
@@ -2286,8 +2362,8 @@
       <c r="W8" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X8" s="1" t="s">
-        <v>103</v>
+      <c r="X8" s="1">
+        <v>2028</v>
       </c>
       <c r="AD8" s="1" t="s">
         <v>104</v>
@@ -2342,12 +2418,12 @@
       </c>
       <c r="AX8" s="2"/>
     </row>
-    <row r="9" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B9" t="s">
-        <v>198</v>
+        <v>370</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>153</v>
@@ -2400,8 +2476,8 @@
       <c r="W9" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="X9" s="1" t="s">
-        <v>110</v>
+      <c r="X9" s="1">
+        <v>2028</v>
       </c>
       <c r="AD9" s="1" t="s">
         <v>104</v>
@@ -2409,12 +2485,12 @@
       <c r="AE9" s="2"/>
       <c r="AX9" s="2"/>
     </row>
-    <row r="10" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B10" t="s">
-        <v>199</v>
+        <v>371</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>153</v>
@@ -2467,8 +2543,8 @@
       <c r="W10" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="X10" s="1" t="s">
-        <v>110</v>
+      <c r="X10" s="1">
+        <v>2028</v>
       </c>
       <c r="AD10" s="1" t="s">
         <v>104</v>
@@ -2476,12 +2552,12 @@
       <c r="AE10" s="2"/>
       <c r="AX10" s="2"/>
     </row>
-    <row r="11" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B11" t="s">
-        <v>200</v>
+        <v>372</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>153</v>
@@ -2540,8 +2616,8 @@
       <c r="W11" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X11" s="1" t="s">
-        <v>103</v>
+      <c r="X11" s="1">
+        <v>2028</v>
       </c>
       <c r="AD11" s="1" t="s">
         <v>104</v>
@@ -2596,12 +2672,12 @@
       </c>
       <c r="AX11" s="2"/>
     </row>
-    <row r="12" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B12" t="s">
-        <v>201</v>
+        <v>373</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>153</v>
@@ -2654,8 +2730,8 @@
       <c r="W12" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="X12" s="1" t="s">
-        <v>110</v>
+      <c r="X12" s="1">
+        <v>2028</v>
       </c>
       <c r="AD12" s="1" t="s">
         <v>104</v>
@@ -2663,12 +2739,12 @@
       <c r="AE12" s="2"/>
       <c r="AX12" s="2"/>
     </row>
-    <row r="13" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B13" t="s">
-        <v>202</v>
+        <v>374</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>153</v>
@@ -2721,8 +2797,8 @@
       <c r="W13" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="X13" s="1" t="s">
-        <v>110</v>
+      <c r="X13" s="1">
+        <v>2028</v>
       </c>
       <c r="AD13" s="1" t="s">
         <v>104</v>
@@ -2730,12 +2806,12 @@
       <c r="AE13" s="2"/>
       <c r="AX13" s="2"/>
     </row>
-    <row r="14" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B14" t="s">
-        <v>203</v>
+        <v>375</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>153</v>
@@ -2794,8 +2870,8 @@
       <c r="W14" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X14" s="1" t="s">
-        <v>103</v>
+      <c r="X14" s="1">
+        <v>2028</v>
       </c>
       <c r="AD14" s="1" t="s">
         <v>104</v>
@@ -2850,12 +2926,12 @@
       </c>
       <c r="AX14" s="2"/>
     </row>
-    <row r="15" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B15" t="s">
-        <v>204</v>
+        <v>376</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>153</v>
@@ -2908,8 +2984,8 @@
       <c r="W15" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="X15" s="1" t="s">
-        <v>110</v>
+      <c r="X15" s="1">
+        <v>2028</v>
       </c>
       <c r="AD15" s="1" t="s">
         <v>104</v>
@@ -2917,12 +2993,12 @@
       <c r="AE15" s="2"/>
       <c r="AX15" s="2"/>
     </row>
-    <row r="16" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B16" t="s">
-        <v>205</v>
+        <v>377</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>153</v>
@@ -2975,8 +3051,8 @@
       <c r="W16" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="X16" s="1" t="s">
-        <v>110</v>
+      <c r="X16" s="1">
+        <v>2028</v>
       </c>
       <c r="AD16" s="1" t="s">
         <v>104</v>
@@ -2984,12 +3060,12 @@
       <c r="AE16" s="2"/>
       <c r="AX16" s="2"/>
     </row>
-    <row r="17" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B17" t="s">
-        <v>206</v>
+        <v>378</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>153</v>
@@ -3048,8 +3124,8 @@
       <c r="W17" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X17" s="1" t="s">
-        <v>103</v>
+      <c r="X17" s="1">
+        <v>2028</v>
       </c>
       <c r="AD17" s="1" t="s">
         <v>104</v>
@@ -3104,12 +3180,12 @@
       </c>
       <c r="AX17" s="2"/>
     </row>
-    <row r="18" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B18" t="s">
-        <v>207</v>
+        <v>379</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>153</v>
@@ -3162,8 +3238,8 @@
       <c r="W18" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="X18" s="1" t="s">
-        <v>110</v>
+      <c r="X18" s="1">
+        <v>2028</v>
       </c>
       <c r="AD18" s="1" t="s">
         <v>104</v>
@@ -3171,12 +3247,12 @@
       <c r="AE18" s="2"/>
       <c r="AX18" s="2"/>
     </row>
-    <row r="19" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B19" t="s">
-        <v>208</v>
+        <v>380</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>153</v>
@@ -3229,8 +3305,8 @@
       <c r="W19" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="X19" s="1" t="s">
-        <v>110</v>
+      <c r="X19" s="1">
+        <v>2028</v>
       </c>
       <c r="AD19" s="1" t="s">
         <v>104</v>
@@ -3238,12 +3314,12 @@
       <c r="AE19" s="2"/>
       <c r="AX19" s="2"/>
     </row>
-    <row r="20" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B20" t="s">
-        <v>209</v>
+        <v>381</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>153</v>
@@ -3302,8 +3378,8 @@
       <c r="W20" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X20" s="1" t="s">
-        <v>103</v>
+      <c r="X20" s="1">
+        <v>2028</v>
       </c>
       <c r="AD20" s="1" t="s">
         <v>104</v>
@@ -3358,12 +3434,12 @@
       </c>
       <c r="AX20" s="2"/>
     </row>
-    <row r="21" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B21" t="s">
-        <v>210</v>
+        <v>382</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>153</v>
@@ -3416,8 +3492,8 @@
       <c r="W21" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="X21" s="1" t="s">
-        <v>110</v>
+      <c r="X21" s="1">
+        <v>2028</v>
       </c>
       <c r="AD21" s="1" t="s">
         <v>104</v>
@@ -3425,12 +3501,12 @@
       <c r="AE21" s="2"/>
       <c r="AX21" s="2"/>
     </row>
-    <row r="22" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B22" t="s">
-        <v>211</v>
+        <v>383</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>153</v>
@@ -3483,8 +3559,8 @@
       <c r="W22" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="X22" s="1" t="s">
-        <v>110</v>
+      <c r="X22" s="1">
+        <v>2028</v>
       </c>
       <c r="AD22" s="1" t="s">
         <v>104</v>
@@ -3492,12 +3568,12 @@
       <c r="AE22" s="2"/>
       <c r="AX22" s="2"/>
     </row>
-    <row r="23" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B23" t="s">
-        <v>212</v>
+        <v>384</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>153</v>
@@ -3556,8 +3632,8 @@
       <c r="W23" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X23" s="1" t="s">
-        <v>103</v>
+      <c r="X23" s="1">
+        <v>2028</v>
       </c>
       <c r="AD23" s="1" t="s">
         <v>104</v>
@@ -3612,12 +3688,12 @@
       </c>
       <c r="AX23" s="2"/>
     </row>
-    <row r="24" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B24" t="s">
-        <v>213</v>
+        <v>385</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>153</v>
@@ -3670,8 +3746,8 @@
       <c r="W24" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="X24" s="1" t="s">
-        <v>110</v>
+      <c r="X24" s="1">
+        <v>2028</v>
       </c>
       <c r="AD24" s="1" t="s">
         <v>104</v>
@@ -3679,12 +3755,12 @@
       <c r="AE24" s="2"/>
       <c r="AX24" s="2"/>
     </row>
-    <row r="25" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B25" t="s">
-        <v>214</v>
+        <v>386</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>153</v>
@@ -3737,8 +3813,8 @@
       <c r="W25" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="X25" s="1" t="s">
-        <v>110</v>
+      <c r="X25" s="1">
+        <v>2028</v>
       </c>
       <c r="AD25" s="1" t="s">
         <v>104</v>
@@ -3746,12 +3822,12 @@
       <c r="AE25" s="2"/>
       <c r="AX25" s="2"/>
     </row>
-    <row r="26" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>149</v>
       </c>
       <c r="B26" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>153</v>
@@ -3810,8 +3886,8 @@
       <c r="W26" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X26" s="1" t="s">
-        <v>103</v>
+      <c r="X26" s="1">
+        <v>2028</v>
       </c>
       <c r="AD26" s="1" t="s">
         <v>104</v>
@@ -3866,12 +3942,12 @@
       </c>
       <c r="AX26" s="2"/>
     </row>
-    <row r="27" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>149</v>
       </c>
       <c r="B27" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>153</v>
@@ -3924,8 +4000,8 @@
       <c r="W27" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="X27" s="1" t="s">
-        <v>110</v>
+      <c r="X27" s="1">
+        <v>2028</v>
       </c>
       <c r="AD27" s="1" t="s">
         <v>104</v>
@@ -3933,12 +4009,12 @@
       <c r="AE27" s="2"/>
       <c r="AX27" s="2"/>
     </row>
-    <row r="28" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>149</v>
       </c>
       <c r="B28" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>153</v>
@@ -3991,8 +4067,8 @@
       <c r="W28" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="X28" s="1" t="s">
-        <v>110</v>
+      <c r="X28" s="1">
+        <v>2028</v>
       </c>
       <c r="AD28" s="1" t="s">
         <v>104</v>
@@ -4000,12 +4076,12 @@
       <c r="AE28" s="2"/>
       <c r="AX28" s="2"/>
     </row>
-    <row r="29" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>149</v>
       </c>
       <c r="B29" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>153</v>
@@ -4064,8 +4140,8 @@
       <c r="W29" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X29" s="1" t="s">
-        <v>103</v>
+      <c r="X29" s="1">
+        <v>2028</v>
       </c>
       <c r="AD29" s="1" t="s">
         <v>104</v>
@@ -4120,12 +4196,12 @@
       </c>
       <c r="AX29" s="2"/>
     </row>
-    <row r="30" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>149</v>
       </c>
       <c r="B30" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>153</v>
@@ -4178,8 +4254,8 @@
       <c r="W30" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="X30" s="1" t="s">
-        <v>110</v>
+      <c r="X30" s="1">
+        <v>2028</v>
       </c>
       <c r="AD30" s="1" t="s">
         <v>104</v>
@@ -4187,12 +4263,12 @@
       <c r="AE30" s="2"/>
       <c r="AX30" s="2"/>
     </row>
-    <row r="31" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>149</v>
       </c>
       <c r="B31" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>153</v>
@@ -4245,8 +4321,8 @@
       <c r="W31" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="X31" s="1" t="s">
-        <v>110</v>
+      <c r="X31" s="1">
+        <v>2028</v>
       </c>
       <c r="AD31" s="1" t="s">
         <v>104</v>
@@ -4254,12 +4330,12 @@
       <c r="AE31" s="2"/>
       <c r="AX31" s="2"/>
     </row>
-    <row r="32" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>149</v>
       </c>
       <c r="B32" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>153</v>
@@ -4318,8 +4394,8 @@
       <c r="W32" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X32" s="1" t="s">
-        <v>103</v>
+      <c r="X32" s="1">
+        <v>2028</v>
       </c>
       <c r="AD32" s="1" t="s">
         <v>104</v>
@@ -4374,12 +4450,12 @@
       </c>
       <c r="AX32" s="2"/>
     </row>
-    <row r="33" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>149</v>
       </c>
       <c r="B33" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>153</v>
@@ -4432,8 +4508,8 @@
       <c r="W33" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="X33" s="1" t="s">
-        <v>110</v>
+      <c r="X33" s="1">
+        <v>2028</v>
       </c>
       <c r="AD33" s="1" t="s">
         <v>104</v>
@@ -4441,12 +4517,12 @@
       <c r="AE33" s="2"/>
       <c r="AX33" s="2"/>
     </row>
-    <row r="34" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>149</v>
       </c>
       <c r="B34" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>153</v>
@@ -4499,8 +4575,8 @@
       <c r="W34" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="X34" s="1" t="s">
-        <v>110</v>
+      <c r="X34" s="1">
+        <v>2028</v>
       </c>
       <c r="AD34" s="1" t="s">
         <v>104</v>
@@ -4508,12 +4584,12 @@
       <c r="AE34" s="2"/>
       <c r="AX34" s="2"/>
     </row>
-    <row r="35" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>149</v>
       </c>
       <c r="B35" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>153</v>
@@ -4572,8 +4648,8 @@
       <c r="W35" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X35" s="1" t="s">
-        <v>103</v>
+      <c r="X35" s="1">
+        <v>2028</v>
       </c>
       <c r="AD35" s="1" t="s">
         <v>104</v>
@@ -4628,12 +4704,12 @@
       </c>
       <c r="AX35" s="2"/>
     </row>
-    <row r="36" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>149</v>
       </c>
       <c r="B36" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>153</v>
@@ -4686,8 +4762,8 @@
       <c r="W36" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="X36" s="1" t="s">
-        <v>110</v>
+      <c r="X36" s="1">
+        <v>2028</v>
       </c>
       <c r="AD36" s="1" t="s">
         <v>104</v>
@@ -4695,12 +4771,12 @@
       <c r="AE36" s="2"/>
       <c r="AX36" s="2"/>
     </row>
-    <row r="37" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>149</v>
       </c>
       <c r="B37" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>153</v>
@@ -4753,8 +4829,8 @@
       <c r="W37" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="X37" s="1" t="s">
-        <v>110</v>
+      <c r="X37" s="1">
+        <v>2028</v>
       </c>
       <c r="AD37" s="1" t="s">
         <v>104</v>
@@ -4762,7 +4838,7 @@
       <c r="AE37" s="2"/>
       <c r="AX37" s="2"/>
     </row>
-    <row r="38" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A38" s="3" t="s">
         <v>150</v>
       </c>
@@ -4826,8 +4902,8 @@
       <c r="W38" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X38" s="1" t="s">
-        <v>103</v>
+      <c r="X38" s="1">
+        <v>2028</v>
       </c>
       <c r="AD38" s="1" t="s">
         <v>104</v>
@@ -4882,12 +4958,12 @@
       </c>
       <c r="AX38" s="2"/>
     </row>
-    <row r="39" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>150</v>
       </c>
       <c r="B39" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>187</v>
@@ -4940,8 +5016,8 @@
       <c r="W39" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="X39" s="1" t="s">
-        <v>110</v>
+      <c r="X39" s="1">
+        <v>2028</v>
       </c>
       <c r="AD39" s="1" t="s">
         <v>104</v>
@@ -4949,12 +5025,12 @@
       <c r="AE39" s="2"/>
       <c r="AX39" s="2"/>
     </row>
-    <row r="40" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>150</v>
       </c>
       <c r="B40" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>187</v>
@@ -5007,8 +5083,8 @@
       <c r="W40" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="X40" s="1" t="s">
-        <v>110</v>
+      <c r="X40" s="1">
+        <v>2028</v>
       </c>
       <c r="AD40" s="1" t="s">
         <v>104</v>
@@ -5016,12 +5092,12 @@
       <c r="AE40" s="2"/>
       <c r="AX40" s="2"/>
     </row>
-    <row r="41" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>150</v>
       </c>
       <c r="B41" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>187</v>
@@ -5080,8 +5156,8 @@
       <c r="W41" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X41" s="1" t="s">
-        <v>103</v>
+      <c r="X41" s="1">
+        <v>2028</v>
       </c>
       <c r="AD41" s="1" t="s">
         <v>104</v>
@@ -5136,12 +5212,12 @@
       </c>
       <c r="AX41" s="2"/>
     </row>
-    <row r="42" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>150</v>
       </c>
       <c r="B42" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>187</v>
@@ -5194,8 +5270,8 @@
       <c r="W42" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="X42" s="1" t="s">
-        <v>110</v>
+      <c r="X42" s="1">
+        <v>2028</v>
       </c>
       <c r="AD42" s="1" t="s">
         <v>104</v>
@@ -5203,12 +5279,12 @@
       <c r="AE42" s="2"/>
       <c r="AX42" s="2"/>
     </row>
-    <row r="43" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>150</v>
       </c>
       <c r="B43" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>187</v>
@@ -5261,8 +5337,8 @@
       <c r="W43" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="X43" s="1" t="s">
-        <v>110</v>
+      <c r="X43" s="1">
+        <v>2028</v>
       </c>
       <c r="AD43" s="1" t="s">
         <v>104</v>
@@ -5270,12 +5346,12 @@
       <c r="AE43" s="2"/>
       <c r="AX43" s="2"/>
     </row>
-    <row r="44" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>150</v>
       </c>
       <c r="B44" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>187</v>
@@ -5334,8 +5410,8 @@
       <c r="W44" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X44" s="1" t="s">
-        <v>103</v>
+      <c r="X44" s="1">
+        <v>2028</v>
       </c>
       <c r="AD44" s="1" t="s">
         <v>104</v>
@@ -5390,12 +5466,12 @@
       </c>
       <c r="AX44" s="2"/>
     </row>
-    <row r="45" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>150</v>
       </c>
       <c r="B45" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>187</v>
@@ -5448,8 +5524,8 @@
       <c r="W45" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="X45" s="1" t="s">
-        <v>110</v>
+      <c r="X45" s="1">
+        <v>2028</v>
       </c>
       <c r="AD45" s="1" t="s">
         <v>104</v>
@@ -5457,12 +5533,12 @@
       <c r="AE45" s="2"/>
       <c r="AX45" s="2"/>
     </row>
-    <row r="46" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>150</v>
       </c>
       <c r="B46" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>187</v>
@@ -5515,8 +5591,8 @@
       <c r="W46" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="X46" s="1" t="s">
-        <v>110</v>
+      <c r="X46" s="1">
+        <v>2028</v>
       </c>
       <c r="AD46" s="1" t="s">
         <v>104</v>
@@ -5524,12 +5600,12 @@
       <c r="AE46" s="2"/>
       <c r="AX46" s="2"/>
     </row>
-    <row r="47" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>150</v>
       </c>
       <c r="B47" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>187</v>
@@ -5588,8 +5664,8 @@
       <c r="W47" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X47" s="1" t="s">
-        <v>103</v>
+      <c r="X47" s="1">
+        <v>2028</v>
       </c>
       <c r="AD47" s="1" t="s">
         <v>104</v>
@@ -5644,12 +5720,12 @@
       </c>
       <c r="AX47" s="2"/>
     </row>
-    <row r="48" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>150</v>
       </c>
       <c r="B48" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>187</v>
@@ -5702,8 +5778,8 @@
       <c r="W48" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="X48" s="1" t="s">
-        <v>110</v>
+      <c r="X48" s="1">
+        <v>2028</v>
       </c>
       <c r="AD48" s="1" t="s">
         <v>104</v>
@@ -5711,12 +5787,12 @@
       <c r="AE48" s="2"/>
       <c r="AX48" s="2"/>
     </row>
-    <row r="49" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>150</v>
       </c>
       <c r="B49" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>187</v>
@@ -5769,8 +5845,8 @@
       <c r="W49" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="X49" s="1" t="s">
-        <v>110</v>
+      <c r="X49" s="1">
+        <v>2028</v>
       </c>
       <c r="AD49" s="1" t="s">
         <v>104</v>
@@ -5778,12 +5854,12 @@
       <c r="AE49" s="2"/>
       <c r="AX49" s="2"/>
     </row>
-    <row r="50" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>149</v>
       </c>
       <c r="B50" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>154</v>
@@ -5836,8 +5912,8 @@
       <c r="W50" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="X50" s="1" t="s">
-        <v>110</v>
+      <c r="X50" s="1">
+        <v>2028</v>
       </c>
       <c r="AD50" s="1" t="s">
         <v>104</v>
@@ -5856,12 +5932,12 @@
         <v>131</v>
       </c>
     </row>
-    <row r="51" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>149</v>
       </c>
       <c r="B51" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>154</v>
@@ -5920,8 +5996,8 @@
       <c r="W51" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X51" s="1" t="s">
-        <v>103</v>
+      <c r="X51" s="1">
+        <v>2028</v>
       </c>
       <c r="AD51" s="1" t="s">
         <v>104</v>
@@ -5987,12 +6063,12 @@
         <v>131</v>
       </c>
     </row>
-    <row r="52" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>149</v>
       </c>
       <c r="B52" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>154</v>
@@ -6045,8 +6121,8 @@
       <c r="W52" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="X52" s="1" t="s">
-        <v>110</v>
+      <c r="X52" s="1">
+        <v>2028</v>
       </c>
       <c r="AD52" s="1" t="s">
         <v>104</v>
@@ -6065,12 +6141,12 @@
         <v>131</v>
       </c>
     </row>
-    <row r="53" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>149</v>
       </c>
       <c r="B53" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>154</v>
@@ -6129,8 +6205,8 @@
       <c r="W53" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X53" s="1" t="s">
-        <v>103</v>
+      <c r="X53" s="1">
+        <v>2028</v>
       </c>
       <c r="AD53" s="1" t="s">
         <v>104</v>
@@ -6196,12 +6272,12 @@
         <v>131</v>
       </c>
     </row>
-    <row r="54" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>149</v>
       </c>
       <c r="B54" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>154</v>
@@ -6254,8 +6330,8 @@
       <c r="W54" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="X54" s="1" t="s">
-        <v>110</v>
+      <c r="X54" s="1">
+        <v>2028</v>
       </c>
       <c r="AD54" s="1" t="s">
         <v>104</v>
@@ -6274,12 +6350,12 @@
         <v>131</v>
       </c>
     </row>
-    <row r="55" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>149</v>
       </c>
       <c r="B55" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>154</v>
@@ -6338,8 +6414,8 @@
       <c r="W55" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X55" s="1" t="s">
-        <v>103</v>
+      <c r="X55" s="1">
+        <v>2028</v>
       </c>
       <c r="AD55" s="1" t="s">
         <v>104</v>
@@ -6405,12 +6481,12 @@
         <v>131</v>
       </c>
     </row>
-    <row r="56" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>149</v>
       </c>
       <c r="B56" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>154</v>
@@ -6463,8 +6539,8 @@
       <c r="W56" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="X56" s="1" t="s">
-        <v>110</v>
+      <c r="X56" s="1">
+        <v>2028</v>
       </c>
       <c r="AD56" s="1" t="s">
         <v>104</v>
@@ -6483,12 +6559,12 @@
         <v>131</v>
       </c>
     </row>
-    <row r="57" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>149</v>
       </c>
       <c r="B57" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>154</v>
@@ -6547,8 +6623,8 @@
       <c r="W57" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X57" s="1" t="s">
-        <v>103</v>
+      <c r="X57" s="1">
+        <v>2028</v>
       </c>
       <c r="AD57" s="1" t="s">
         <v>104</v>
@@ -6614,12 +6690,12 @@
         <v>131</v>
       </c>
     </row>
-    <row r="58" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>149</v>
       </c>
       <c r="B58" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>154</v>
@@ -6672,8 +6748,8 @@
       <c r="W58" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="X58" s="1" t="s">
-        <v>110</v>
+      <c r="X58" s="1">
+        <v>2028</v>
       </c>
       <c r="AD58" s="1" t="s">
         <v>104</v>
@@ -6692,12 +6768,12 @@
         <v>131</v>
       </c>
     </row>
-    <row r="59" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>149</v>
       </c>
       <c r="B59" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>154</v>
@@ -6756,8 +6832,8 @@
       <c r="W59" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X59" s="1" t="s">
-        <v>103</v>
+      <c r="X59" s="1">
+        <v>2028</v>
       </c>
       <c r="AD59" s="1" t="s">
         <v>104</v>
@@ -6823,12 +6899,12 @@
         <v>131</v>
       </c>
     </row>
-    <row r="60" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>149</v>
       </c>
       <c r="B60" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>154</v>
@@ -6881,8 +6957,8 @@
       <c r="W60" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="X60" s="1" t="s">
-        <v>110</v>
+      <c r="X60" s="1">
+        <v>2028</v>
       </c>
       <c r="AD60" s="1" t="s">
         <v>104</v>
@@ -6901,12 +6977,12 @@
         <v>131</v>
       </c>
     </row>
-    <row r="61" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>149</v>
       </c>
       <c r="B61" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>154</v>
@@ -6965,8 +7041,8 @@
       <c r="W61" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X61" s="1" t="s">
-        <v>103</v>
+      <c r="X61" s="1">
+        <v>2028</v>
       </c>
       <c r="AD61" s="1" t="s">
         <v>104</v>
@@ -7032,7 +7108,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="62" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A62" s="3" t="s">
         <v>150</v>
       </c>
@@ -7040,7 +7116,7 @@
         <v>172</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>177</v>
@@ -7096,8 +7172,8 @@
       <c r="W62" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X62" s="1" t="s">
-        <v>103</v>
+      <c r="X62" s="1">
+        <v>2028</v>
       </c>
       <c r="AD62" s="1" t="s">
         <v>104</v>
@@ -7163,15 +7239,15 @@
         <v>131</v>
       </c>
     </row>
-    <row r="63" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>150</v>
       </c>
       <c r="B63" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>152</v>
@@ -7221,8 +7297,8 @@
       <c r="W63" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="X63" s="1" t="s">
-        <v>110</v>
+      <c r="X63" s="1">
+        <v>2028</v>
       </c>
       <c r="AD63" s="1" t="s">
         <v>104</v>
@@ -7241,15 +7317,15 @@
         <v>131</v>
       </c>
     </row>
-    <row r="64" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>150</v>
       </c>
       <c r="B64" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>152</v>
@@ -7299,8 +7375,8 @@
       <c r="W64" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="X64" s="1" t="s">
-        <v>110</v>
+      <c r="X64" s="1">
+        <v>2028</v>
       </c>
       <c r="AD64" s="1" t="s">
         <v>104</v>
@@ -7319,15 +7395,15 @@
         <v>131</v>
       </c>
     </row>
-    <row r="65" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
         <v>150</v>
       </c>
       <c r="B65" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>152</v>
@@ -7383,8 +7459,8 @@
       <c r="W65" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X65" s="1" t="s">
-        <v>103</v>
+      <c r="X65" s="1">
+        <v>2028</v>
       </c>
       <c r="AD65" s="1" t="s">
         <v>104</v>
@@ -7450,15 +7526,15 @@
         <v>131</v>
       </c>
     </row>
-    <row r="66" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
         <v>150</v>
       </c>
       <c r="B66" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>152</v>
@@ -7508,8 +7584,8 @@
       <c r="W66" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="X66" s="1" t="s">
-        <v>110</v>
+      <c r="X66" s="1">
+        <v>2028</v>
       </c>
       <c r="AD66" s="1" t="s">
         <v>104</v>
@@ -7528,15 +7604,15 @@
         <v>131</v>
       </c>
     </row>
-    <row r="67" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
         <v>150</v>
       </c>
       <c r="B67" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>152</v>
@@ -7586,8 +7662,8 @@
       <c r="W67" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="X67" s="1" t="s">
-        <v>110</v>
+      <c r="X67" s="1">
+        <v>2028</v>
       </c>
       <c r="AD67" s="1" t="s">
         <v>104</v>
@@ -7606,15 +7682,15 @@
         <v>131</v>
       </c>
     </row>
-    <row r="68" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
         <v>150</v>
       </c>
       <c r="B68" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>152</v>
@@ -7670,8 +7746,8 @@
       <c r="W68" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X68" s="1" t="s">
-        <v>103</v>
+      <c r="X68" s="1">
+        <v>2028</v>
       </c>
       <c r="AD68" s="1" t="s">
         <v>104</v>
@@ -7737,15 +7813,15 @@
         <v>131</v>
       </c>
     </row>
-    <row r="69" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
         <v>150</v>
       </c>
       <c r="B69" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>152</v>
@@ -7795,8 +7871,8 @@
       <c r="W69" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="X69" s="1" t="s">
-        <v>110</v>
+      <c r="X69" s="1">
+        <v>2028</v>
       </c>
       <c r="AD69" s="1" t="s">
         <v>104</v>
@@ -7815,15 +7891,15 @@
         <v>131</v>
       </c>
     </row>
-    <row r="70" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
         <v>150</v>
       </c>
       <c r="B70" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>152</v>
@@ -7873,8 +7949,8 @@
       <c r="W70" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="X70" s="1" t="s">
-        <v>110</v>
+      <c r="X70" s="1">
+        <v>2028</v>
       </c>
       <c r="AD70" s="1" t="s">
         <v>104</v>
@@ -7893,15 +7969,15 @@
         <v>131</v>
       </c>
     </row>
-    <row r="71" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
         <v>150</v>
       </c>
       <c r="B71" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>152</v>
@@ -7957,8 +8033,8 @@
       <c r="W71" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X71" s="1" t="s">
-        <v>103</v>
+      <c r="X71" s="1">
+        <v>2028</v>
       </c>
       <c r="AD71" s="1" t="s">
         <v>104</v>
@@ -8024,15 +8100,15 @@
         <v>131</v>
       </c>
     </row>
-    <row r="72" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
         <v>150</v>
       </c>
       <c r="B72" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>152</v>
@@ -8082,8 +8158,8 @@
       <c r="W72" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="X72" s="1" t="s">
-        <v>110</v>
+      <c r="X72" s="1">
+        <v>2028</v>
       </c>
       <c r="AD72" s="1" t="s">
         <v>104</v>
@@ -8102,15 +8178,15 @@
         <v>131</v>
       </c>
     </row>
-    <row r="73" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
         <v>150</v>
       </c>
       <c r="B73" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>152</v>
@@ -8160,8 +8236,8 @@
       <c r="W73" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="X73" s="1" t="s">
-        <v>110</v>
+      <c r="X73" s="1">
+        <v>2028</v>
       </c>
       <c r="AD73" s="1" t="s">
         <v>104</v>
@@ -8180,12 +8256,12 @@
         <v>131</v>
       </c>
     </row>
-    <row r="74" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
         <v>149</v>
       </c>
       <c r="B74" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>155</v>
@@ -8238,8 +8314,8 @@
       <c r="W74" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="X74" s="1" t="s">
-        <v>110</v>
+      <c r="X74" s="1">
+        <v>2028</v>
       </c>
       <c r="AD74" s="1" t="s">
         <v>104</v>
@@ -8258,12 +8334,12 @@
         <v>132</v>
       </c>
     </row>
-    <row r="75" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
         <v>149</v>
       </c>
       <c r="B75" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>155</v>
@@ -8322,8 +8398,8 @@
       <c r="W75" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X75" s="1" t="s">
-        <v>103</v>
+      <c r="X75" s="1">
+        <v>2028</v>
       </c>
       <c r="AD75" s="1" t="s">
         <v>104</v>
@@ -8389,12 +8465,12 @@
         <v>132</v>
       </c>
     </row>
-    <row r="76" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
         <v>149</v>
       </c>
       <c r="B76" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>155</v>
@@ -8447,8 +8523,8 @@
       <c r="W76" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="X76" s="1" t="s">
-        <v>110</v>
+      <c r="X76" s="1">
+        <v>2028</v>
       </c>
       <c r="AD76" s="1" t="s">
         <v>104</v>
@@ -8467,12 +8543,12 @@
         <v>132</v>
       </c>
     </row>
-    <row r="77" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
         <v>149</v>
       </c>
       <c r="B77" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>155</v>
@@ -8531,8 +8607,8 @@
       <c r="W77" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X77" s="1" t="s">
-        <v>103</v>
+      <c r="X77" s="1">
+        <v>2028</v>
       </c>
       <c r="AD77" s="1" t="s">
         <v>104</v>
@@ -8598,12 +8674,12 @@
         <v>132</v>
       </c>
     </row>
-    <row r="78" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
         <v>149</v>
       </c>
       <c r="B78" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>155</v>
@@ -8656,8 +8732,8 @@
       <c r="W78" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="X78" s="1" t="s">
-        <v>110</v>
+      <c r="X78" s="1">
+        <v>2028</v>
       </c>
       <c r="AD78" s="1" t="s">
         <v>104</v>
@@ -8676,12 +8752,12 @@
         <v>132</v>
       </c>
     </row>
-    <row r="79" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
         <v>149</v>
       </c>
       <c r="B79" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>155</v>
@@ -8740,8 +8816,8 @@
       <c r="W79" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X79" s="1" t="s">
-        <v>103</v>
+      <c r="X79" s="1">
+        <v>2028</v>
       </c>
       <c r="AD79" s="1" t="s">
         <v>104</v>
@@ -8807,12 +8883,12 @@
         <v>132</v>
       </c>
     </row>
-    <row r="80" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
         <v>149</v>
       </c>
       <c r="B80" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>155</v>
@@ -8865,8 +8941,8 @@
       <c r="W80" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="X80" s="1" t="s">
-        <v>110</v>
+      <c r="X80" s="1">
+        <v>2028</v>
       </c>
       <c r="AD80" s="1" t="s">
         <v>104</v>
@@ -8885,12 +8961,12 @@
         <v>132</v>
       </c>
     </row>
-    <row r="81" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
         <v>149</v>
       </c>
       <c r="B81" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>155</v>
@@ -8949,8 +9025,8 @@
       <c r="W81" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X81" s="1" t="s">
-        <v>103</v>
+      <c r="X81" s="1">
+        <v>2028</v>
       </c>
       <c r="AD81" s="1" t="s">
         <v>104</v>
@@ -9016,12 +9092,12 @@
         <v>132</v>
       </c>
     </row>
-    <row r="82" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
         <v>149</v>
       </c>
       <c r="B82" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>155</v>
@@ -9074,8 +9150,8 @@
       <c r="W82" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="X82" s="1" t="s">
-        <v>110</v>
+      <c r="X82" s="1">
+        <v>2028</v>
       </c>
       <c r="AD82" s="1" t="s">
         <v>104</v>
@@ -9094,12 +9170,12 @@
         <v>132</v>
       </c>
     </row>
-    <row r="83" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
         <v>149</v>
       </c>
       <c r="B83" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>155</v>
@@ -9158,8 +9234,8 @@
       <c r="W83" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X83" s="1" t="s">
-        <v>103</v>
+      <c r="X83" s="1">
+        <v>2028</v>
       </c>
       <c r="AD83" s="1" t="s">
         <v>104</v>
@@ -9225,12 +9301,12 @@
         <v>132</v>
       </c>
     </row>
-    <row r="84" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
         <v>149</v>
       </c>
       <c r="B84" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>155</v>
@@ -9283,8 +9359,8 @@
       <c r="W84" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="X84" s="1" t="s">
-        <v>110</v>
+      <c r="X84" s="1">
+        <v>2028</v>
       </c>
       <c r="AD84" s="1" t="s">
         <v>104</v>
@@ -9303,12 +9379,12 @@
         <v>132</v>
       </c>
     </row>
-    <row r="85" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
         <v>149</v>
       </c>
       <c r="B85" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>155</v>
@@ -9367,8 +9443,8 @@
       <c r="W85" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X85" s="1" t="s">
-        <v>103</v>
+      <c r="X85" s="1">
+        <v>2028</v>
       </c>
       <c r="AD85" s="1" t="s">
         <v>104</v>
@@ -9434,7 +9510,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="86" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A86" s="3" t="s">
         <v>150</v>
       </c>
@@ -9442,7 +9518,7 @@
         <v>173</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>177</v>
@@ -9498,8 +9574,8 @@
       <c r="W86" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X86" s="1" t="s">
-        <v>103</v>
+      <c r="X86" s="1">
+        <v>2028</v>
       </c>
       <c r="AD86" s="1" t="s">
         <v>104</v>
@@ -9565,15 +9641,15 @@
         <v>132</v>
       </c>
     </row>
-    <row r="87" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
         <v>150</v>
       </c>
       <c r="B87" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>152</v>
@@ -9623,8 +9699,8 @@
       <c r="W87" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="X87" s="1" t="s">
-        <v>110</v>
+      <c r="X87" s="1">
+        <v>2028</v>
       </c>
       <c r="AD87" s="1" t="s">
         <v>104</v>
@@ -9643,15 +9719,15 @@
         <v>132</v>
       </c>
     </row>
-    <row r="88" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
         <v>150</v>
       </c>
       <c r="B88" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>152</v>
@@ -9701,8 +9777,8 @@
       <c r="W88" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="X88" s="1" t="s">
-        <v>110</v>
+      <c r="X88" s="1">
+        <v>2028</v>
       </c>
       <c r="AD88" s="1" t="s">
         <v>104</v>
@@ -9721,15 +9797,15 @@
         <v>132</v>
       </c>
     </row>
-    <row r="89" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
         <v>150</v>
       </c>
       <c r="B89" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>152</v>
@@ -9785,8 +9861,8 @@
       <c r="W89" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X89" s="1" t="s">
-        <v>103</v>
+      <c r="X89" s="1">
+        <v>2028</v>
       </c>
       <c r="AD89" s="1" t="s">
         <v>104</v>
@@ -9852,15 +9928,15 @@
         <v>132</v>
       </c>
     </row>
-    <row r="90" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
         <v>150</v>
       </c>
       <c r="B90" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>152</v>
@@ -9910,8 +9986,8 @@
       <c r="W90" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="X90" s="1" t="s">
-        <v>110</v>
+      <c r="X90" s="1">
+        <v>2028</v>
       </c>
       <c r="AD90" s="1" t="s">
         <v>104</v>
@@ -9930,15 +10006,15 @@
         <v>132</v>
       </c>
     </row>
-    <row r="91" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
         <v>150</v>
       </c>
       <c r="B91" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>152</v>
@@ -9988,8 +10064,8 @@
       <c r="W91" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="X91" s="1" t="s">
-        <v>110</v>
+      <c r="X91" s="1">
+        <v>2028</v>
       </c>
       <c r="AD91" s="1" t="s">
         <v>104</v>
@@ -10008,15 +10084,15 @@
         <v>132</v>
       </c>
     </row>
-    <row r="92" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
         <v>150</v>
       </c>
       <c r="B92" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D92" s="1" t="s">
         <v>152</v>
@@ -10072,8 +10148,8 @@
       <c r="W92" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X92" s="1" t="s">
-        <v>103</v>
+      <c r="X92" s="1">
+        <v>2028</v>
       </c>
       <c r="AD92" s="1" t="s">
         <v>104</v>
@@ -10139,15 +10215,15 @@
         <v>132</v>
       </c>
     </row>
-    <row r="93" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
         <v>150</v>
       </c>
       <c r="B93" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>152</v>
@@ -10197,8 +10273,8 @@
       <c r="W93" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="X93" s="1" t="s">
-        <v>110</v>
+      <c r="X93" s="1">
+        <v>2028</v>
       </c>
       <c r="AD93" s="1" t="s">
         <v>104</v>
@@ -10217,15 +10293,15 @@
         <v>132</v>
       </c>
     </row>
-    <row r="94" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
         <v>150</v>
       </c>
       <c r="B94" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>152</v>
@@ -10275,8 +10351,8 @@
       <c r="W94" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="X94" s="1" t="s">
-        <v>110</v>
+      <c r="X94" s="1">
+        <v>2028</v>
       </c>
       <c r="AD94" s="1" t="s">
         <v>104</v>
@@ -10295,15 +10371,15 @@
         <v>132</v>
       </c>
     </row>
-    <row r="95" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
         <v>150</v>
       </c>
       <c r="B95" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>152</v>
@@ -10359,8 +10435,8 @@
       <c r="W95" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X95" s="1" t="s">
-        <v>103</v>
+      <c r="X95" s="1">
+        <v>2028</v>
       </c>
       <c r="AD95" s="1" t="s">
         <v>104</v>
@@ -10426,15 +10502,15 @@
         <v>132</v>
       </c>
     </row>
-    <row r="96" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
         <v>150</v>
       </c>
       <c r="B96" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>152</v>
@@ -10484,8 +10560,8 @@
       <c r="W96" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="X96" s="1" t="s">
-        <v>110</v>
+      <c r="X96" s="1">
+        <v>2028</v>
       </c>
       <c r="AD96" s="1" t="s">
         <v>104</v>
@@ -10504,15 +10580,15 @@
         <v>132</v>
       </c>
     </row>
-    <row r="97" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
         <v>150</v>
       </c>
       <c r="B97" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>152</v>
@@ -10562,8 +10638,8 @@
       <c r="W97" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="X97" s="1" t="s">
-        <v>110</v>
+      <c r="X97" s="1">
+        <v>2028</v>
       </c>
       <c r="AD97" s="1" t="s">
         <v>104</v>
@@ -10582,12 +10658,12 @@
         <v>132</v>
       </c>
     </row>
-    <row r="98" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
         <v>149</v>
       </c>
       <c r="B98" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>156</v>
@@ -10634,18 +10710,18 @@
       <c r="W98" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X98" s="1" t="s">
-        <v>103</v>
+      <c r="X98" s="1">
+        <v>2028</v>
       </c>
       <c r="AE98" s="2"/>
       <c r="AX98" s="2"/>
     </row>
-    <row r="99" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A99" t="s">
         <v>149</v>
       </c>
       <c r="B99" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>156</v>
@@ -10692,18 +10768,18 @@
       <c r="W99" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X99" s="1" t="s">
-        <v>103</v>
+      <c r="X99" s="1">
+        <v>2028</v>
       </c>
       <c r="AE99" s="2"/>
       <c r="AX99" s="2"/>
     </row>
-    <row r="100" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
         <v>149</v>
       </c>
       <c r="B100" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>156</v>
@@ -10750,21 +10826,21 @@
       <c r="W100" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X100" s="1" t="s">
-        <v>103</v>
+      <c r="X100" s="1">
+        <v>2028</v>
       </c>
       <c r="AE100" s="2"/>
       <c r="AX100" s="2"/>
     </row>
-    <row r="101" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
         <v>150</v>
       </c>
       <c r="B101" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D101" s="1" t="s">
         <v>152</v>
@@ -10808,21 +10884,21 @@
       <c r="W101" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X101" s="1" t="s">
-        <v>103</v>
+      <c r="X101" s="1">
+        <v>2028</v>
       </c>
       <c r="AE101" s="2"/>
       <c r="AX101" s="2"/>
     </row>
-    <row r="102" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
         <v>150</v>
       </c>
       <c r="B102" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D102" s="1" t="s">
         <v>152</v>
@@ -10866,21 +10942,21 @@
       <c r="W102" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="X102" s="1" t="s">
-        <v>110</v>
+      <c r="X102" s="1">
+        <v>2028</v>
       </c>
       <c r="AE102" s="2"/>
       <c r="AX102" s="2"/>
     </row>
-    <row r="103" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A103" t="s">
         <v>150</v>
       </c>
       <c r="B103" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D103" s="1" t="s">
         <v>152</v>
@@ -10924,18 +11000,18 @@
       <c r="W103" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="X103" s="1" t="s">
-        <v>110</v>
+      <c r="X103" s="1">
+        <v>2028</v>
       </c>
       <c r="AE103" s="2"/>
       <c r="AX103" s="2"/>
     </row>
-    <row r="104" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A104" t="s">
         <v>149</v>
       </c>
       <c r="B104" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>157</v>
@@ -10973,7 +11049,7 @@
       <c r="AE104" s="2"/>
       <c r="AX104" s="2"/>
     </row>
-    <row r="105" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A105" s="3" t="s">
         <v>150</v>
       </c>
@@ -11016,12 +11092,12 @@
       <c r="AE105" s="2"/>
       <c r="AX105" s="2"/>
     </row>
-    <row r="106" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A106" t="s">
         <v>149</v>
       </c>
       <c r="B106" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>159</v>
@@ -11062,12 +11138,12 @@
       <c r="AE106" s="2"/>
       <c r="AX106" s="2"/>
     </row>
-    <row r="107" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A107" t="s">
         <v>149</v>
       </c>
       <c r="B107" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>160</v>
@@ -11108,12 +11184,12 @@
       <c r="AE107" s="2"/>
       <c r="AX107" s="2"/>
     </row>
-    <row r="108" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A108" t="s">
         <v>149</v>
       </c>
       <c r="B108" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>157</v>
@@ -11151,7 +11227,7 @@
       <c r="AE108" s="2"/>
       <c r="AX108" s="2"/>
     </row>
-    <row r="109" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A109" s="3" t="s">
         <v>150</v>
       </c>
@@ -11194,12 +11270,12 @@
       <c r="AE109" s="2"/>
       <c r="AX109" s="2"/>
     </row>
-    <row r="110" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A110" t="s">
         <v>149</v>
       </c>
       <c r="B110" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>159</v>
@@ -11240,12 +11316,12 @@
       <c r="AE110" s="2"/>
       <c r="AX110" s="2"/>
     </row>
-    <row r="111" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A111" t="s">
         <v>149</v>
       </c>
       <c r="B111" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>160</v>
@@ -11286,12 +11362,12 @@
       <c r="AE111" s="2"/>
       <c r="AX111" s="2"/>
     </row>
-    <row r="112" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A112" t="s">
         <v>149</v>
       </c>
       <c r="B112" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>157</v>
@@ -11329,7 +11405,7 @@
       <c r="AE112" s="2"/>
       <c r="AX112" s="2"/>
     </row>
-    <row r="113" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A113" s="3" t="s">
         <v>150</v>
       </c>
@@ -11372,12 +11448,12 @@
       <c r="AE113" s="2"/>
       <c r="AX113" s="2"/>
     </row>
-    <row r="114" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
         <v>149</v>
       </c>
       <c r="B114" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>159</v>
@@ -11418,12 +11494,12 @@
       <c r="AE114" s="2"/>
       <c r="AX114" s="2"/>
     </row>
-    <row r="115" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A115" t="s">
         <v>149</v>
       </c>
       <c r="B115" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>160</v>
@@ -11464,12 +11540,12 @@
       <c r="AE115" s="2"/>
       <c r="AX115" s="2"/>
     </row>
-    <row r="116" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A116" t="s">
         <v>150</v>
       </c>
       <c r="B116" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>161</v>
@@ -11528,8 +11604,8 @@
       <c r="W116" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X116" s="1" t="s">
-        <v>103</v>
+      <c r="X116" s="1">
+        <v>2028</v>
       </c>
       <c r="AD116" s="1" t="s">
         <v>104</v>
@@ -11584,12 +11660,12 @@
       </c>
       <c r="AX116" s="2"/>
     </row>
-    <row r="117" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A117" t="s">
         <v>150</v>
       </c>
       <c r="B117" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>161</v>
@@ -11648,8 +11724,8 @@
       <c r="W117" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X117" s="1" t="s">
-        <v>103</v>
+      <c r="X117" s="1">
+        <v>2028</v>
       </c>
       <c r="AD117" s="1" t="s">
         <v>104</v>
@@ -11704,12 +11780,12 @@
       </c>
       <c r="AX117" s="2"/>
     </row>
-    <row r="118" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
         <v>150</v>
       </c>
       <c r="B118" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>161</v>
@@ -11768,8 +11844,8 @@
       <c r="W118" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X118" s="1" t="s">
-        <v>103</v>
+      <c r="X118" s="1">
+        <v>2028</v>
       </c>
       <c r="AD118" s="1" t="s">
         <v>104</v>
@@ -11824,12 +11900,12 @@
       </c>
       <c r="AX118" s="2"/>
     </row>
-    <row r="119" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A119" t="s">
         <v>150</v>
       </c>
       <c r="B119" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>161</v>
@@ -11888,8 +11964,8 @@
       <c r="W119" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X119" s="1" t="s">
-        <v>103</v>
+      <c r="X119" s="1">
+        <v>2028</v>
       </c>
       <c r="AD119" s="1" t="s">
         <v>104</v>
@@ -11944,12 +12020,12 @@
       </c>
       <c r="AX119" s="2"/>
     </row>
-    <row r="120" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A120" t="s">
         <v>150</v>
       </c>
       <c r="B120" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>161</v>
@@ -12008,8 +12084,8 @@
       <c r="W120" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X120" s="1" t="s">
-        <v>103</v>
+      <c r="X120" s="1">
+        <v>2028</v>
       </c>
       <c r="AD120" s="1" t="s">
         <v>104</v>
@@ -12064,12 +12140,12 @@
       </c>
       <c r="AX120" s="2"/>
     </row>
-    <row r="121" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A121" t="s">
         <v>150</v>
       </c>
       <c r="B121" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>161</v>
@@ -12128,8 +12204,8 @@
       <c r="W121" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X121" s="1" t="s">
-        <v>103</v>
+      <c r="X121" s="1">
+        <v>2028</v>
       </c>
       <c r="AD121" s="1" t="s">
         <v>104</v>
@@ -12184,12 +12260,12 @@
       </c>
       <c r="AX121" s="2"/>
     </row>
-    <row r="122" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A122" t="s">
         <v>150</v>
       </c>
       <c r="B122" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>161</v>
@@ -12248,8 +12324,8 @@
       <c r="W122" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X122" s="1" t="s">
-        <v>103</v>
+      <c r="X122" s="1">
+        <v>2028</v>
       </c>
       <c r="AD122" s="1" t="s">
         <v>104</v>
@@ -12304,12 +12380,12 @@
       </c>
       <c r="AX122" s="2"/>
     </row>
-    <row r="123" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A123" t="s">
         <v>150</v>
       </c>
       <c r="B123" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>161</v>
@@ -12368,8 +12444,8 @@
       <c r="W123" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X123" s="1" t="s">
-        <v>103</v>
+      <c r="X123" s="1">
+        <v>2028</v>
       </c>
       <c r="AD123" s="1" t="s">
         <v>104</v>
@@ -12424,12 +12500,12 @@
       </c>
       <c r="AX123" s="2"/>
     </row>
-    <row r="124" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A124" t="s">
         <v>150</v>
       </c>
       <c r="B124" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>161</v>
@@ -12488,8 +12564,8 @@
       <c r="W124" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X124" s="1" t="s">
-        <v>103</v>
+      <c r="X124" s="1">
+        <v>2028</v>
       </c>
       <c r="AD124" s="1" t="s">
         <v>104</v>
@@ -12544,12 +12620,12 @@
       </c>
       <c r="AX124" s="2"/>
     </row>
-    <row r="125" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A125" t="s">
         <v>150</v>
       </c>
       <c r="B125" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>161</v>
@@ -12608,8 +12684,8 @@
       <c r="W125" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X125" s="1" t="s">
-        <v>103</v>
+      <c r="X125" s="1">
+        <v>2028</v>
       </c>
       <c r="AD125" s="1" t="s">
         <v>104</v>
@@ -12664,12 +12740,12 @@
       </c>
       <c r="AX125" s="2"/>
     </row>
-    <row r="126" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A126" t="s">
         <v>150</v>
       </c>
       <c r="B126" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>161</v>
@@ -12728,8 +12804,8 @@
       <c r="W126" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X126" s="1" t="s">
-        <v>103</v>
+      <c r="X126" s="1">
+        <v>2028</v>
       </c>
       <c r="AD126" s="1" t="s">
         <v>104</v>
@@ -12784,12 +12860,12 @@
       </c>
       <c r="AX126" s="2"/>
     </row>
-    <row r="127" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A127" t="s">
         <v>150</v>
       </c>
       <c r="B127" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>161</v>
@@ -12848,8 +12924,8 @@
       <c r="W127" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X127" s="1" t="s">
-        <v>103</v>
+      <c r="X127" s="1">
+        <v>2028</v>
       </c>
       <c r="AD127" s="1" t="s">
         <v>104</v>
@@ -12904,12 +12980,12 @@
       </c>
       <c r="AX127" s="2"/>
     </row>
-    <row r="128" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A128" t="s">
         <v>149</v>
       </c>
       <c r="B128" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>170</v>
@@ -12968,8 +13044,8 @@
       <c r="W128" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X128" s="1" t="s">
-        <v>103</v>
+      <c r="X128" s="1">
+        <v>2028</v>
       </c>
       <c r="AD128" s="1" t="s">
         <v>104</v>
@@ -13024,12 +13100,12 @@
       </c>
       <c r="AX128" s="2"/>
     </row>
-    <row r="129" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A129" t="s">
         <v>149</v>
       </c>
       <c r="B129" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>170</v>
@@ -13088,8 +13164,8 @@
       <c r="W129" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X129" s="1" t="s">
-        <v>103</v>
+      <c r="X129" s="1">
+        <v>2028</v>
       </c>
       <c r="AD129" s="1" t="s">
         <v>104</v>
@@ -13144,12 +13220,12 @@
       </c>
       <c r="AX129" s="2"/>
     </row>
-    <row r="130" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A130" t="s">
         <v>149</v>
       </c>
       <c r="B130" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>170</v>
@@ -13208,8 +13284,8 @@
       <c r="W130" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X130" s="1" t="s">
-        <v>103</v>
+      <c r="X130" s="1">
+        <v>2028</v>
       </c>
       <c r="AD130" s="1" t="s">
         <v>104</v>
@@ -13264,12 +13340,12 @@
       </c>
       <c r="AX130" s="2"/>
     </row>
-    <row r="131" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A131" t="s">
         <v>149</v>
       </c>
       <c r="B131" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>170</v>
@@ -13328,8 +13404,8 @@
       <c r="W131" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X131" s="1" t="s">
-        <v>103</v>
+      <c r="X131" s="1">
+        <v>2028</v>
       </c>
       <c r="AD131" s="1" t="s">
         <v>104</v>
@@ -13384,12 +13460,12 @@
       </c>
       <c r="AX131" s="2"/>
     </row>
-    <row r="132" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A132" t="s">
         <v>149</v>
       </c>
       <c r="B132" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>170</v>
@@ -13448,8 +13524,8 @@
       <c r="W132" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X132" s="1" t="s">
-        <v>103</v>
+      <c r="X132" s="1">
+        <v>2028</v>
       </c>
       <c r="AD132" s="1" t="s">
         <v>104</v>
@@ -13504,12 +13580,12 @@
       </c>
       <c r="AX132" s="2"/>
     </row>
-    <row r="133" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A133" t="s">
         <v>149</v>
       </c>
       <c r="B133" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>170</v>
@@ -13568,8 +13644,8 @@
       <c r="W133" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X133" s="1" t="s">
-        <v>103</v>
+      <c r="X133" s="1">
+        <v>2028</v>
       </c>
       <c r="AD133" s="1" t="s">
         <v>104</v>
@@ -13624,12 +13700,12 @@
       </c>
       <c r="AX133" s="2"/>
     </row>
-    <row r="134" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A134" t="s">
         <v>149</v>
       </c>
       <c r="B134" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>170</v>
@@ -13688,8 +13764,8 @@
       <c r="W134" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X134" s="1" t="s">
-        <v>103</v>
+      <c r="X134" s="1">
+        <v>2028</v>
       </c>
       <c r="AD134" s="1" t="s">
         <v>104</v>
@@ -13744,12 +13820,12 @@
       </c>
       <c r="AX134" s="2"/>
     </row>
-    <row r="135" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A135" t="s">
         <v>149</v>
       </c>
       <c r="B135" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>170</v>
@@ -13808,8 +13884,8 @@
       <c r="W135" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X135" s="1" t="s">
-        <v>103</v>
+      <c r="X135" s="1">
+        <v>2028</v>
       </c>
       <c r="AD135" s="1" t="s">
         <v>104</v>
@@ -13864,12 +13940,12 @@
       </c>
       <c r="AX135" s="2"/>
     </row>
-    <row r="136" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
         <v>149</v>
       </c>
       <c r="B136" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>170</v>
@@ -13928,8 +14004,8 @@
       <c r="W136" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X136" s="1" t="s">
-        <v>103</v>
+      <c r="X136" s="1">
+        <v>2028</v>
       </c>
       <c r="AD136" s="1" t="s">
         <v>104</v>
@@ -13984,12 +14060,12 @@
       </c>
       <c r="AX136" s="2"/>
     </row>
-    <row r="137" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A137" t="s">
         <v>149</v>
       </c>
       <c r="B137" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>170</v>
@@ -14048,8 +14124,8 @@
       <c r="W137" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X137" s="1" t="s">
-        <v>103</v>
+      <c r="X137" s="1">
+        <v>2028</v>
       </c>
       <c r="AD137" s="1" t="s">
         <v>104</v>
@@ -14104,12 +14180,12 @@
       </c>
       <c r="AX137" s="2"/>
     </row>
-    <row r="138" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A138" t="s">
         <v>149</v>
       </c>
       <c r="B138" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>170</v>
@@ -14168,8 +14244,8 @@
       <c r="W138" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X138" s="1" t="s">
-        <v>103</v>
+      <c r="X138" s="1">
+        <v>2028</v>
       </c>
       <c r="AD138" s="1" t="s">
         <v>104</v>
@@ -14224,12 +14300,12 @@
       </c>
       <c r="AX138" s="2"/>
     </row>
-    <row r="139" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A139" t="s">
         <v>149</v>
       </c>
       <c r="B139" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>170</v>
@@ -14288,8 +14364,8 @@
       <c r="W139" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X139" s="1" t="s">
-        <v>103</v>
+      <c r="X139" s="1">
+        <v>2028</v>
       </c>
       <c r="AD139" s="1" t="s">
         <v>104</v>
@@ -14344,12 +14420,12 @@
       </c>
       <c r="AX139" s="2"/>
     </row>
-    <row r="140" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A140" t="s">
         <v>149</v>
       </c>
       <c r="B140" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>181</v>
@@ -14408,8 +14484,8 @@
       <c r="W140" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X140" s="1" t="s">
-        <v>103</v>
+      <c r="X140" s="1">
+        <v>2028</v>
       </c>
       <c r="AD140" s="1" t="s">
         <v>104</v>
@@ -14464,12 +14540,12 @@
       </c>
       <c r="AX140" s="2"/>
     </row>
-    <row r="141" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A141" t="s">
         <v>149</v>
       </c>
       <c r="B141" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>181</v>
@@ -14528,8 +14604,8 @@
       <c r="W141" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X141" s="1" t="s">
-        <v>103</v>
+      <c r="X141" s="1">
+        <v>2028</v>
       </c>
       <c r="AD141" s="1" t="s">
         <v>104</v>
@@ -14584,12 +14660,12 @@
       </c>
       <c r="AX141" s="2"/>
     </row>
-    <row r="142" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A142" t="s">
         <v>149</v>
       </c>
       <c r="B142" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>181</v>
@@ -14648,8 +14724,8 @@
       <c r="W142" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X142" s="1" t="s">
-        <v>103</v>
+      <c r="X142" s="1">
+        <v>2028</v>
       </c>
       <c r="AD142" s="1" t="s">
         <v>104</v>
@@ -14704,12 +14780,12 @@
       </c>
       <c r="AX142" s="2"/>
     </row>
-    <row r="143" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A143" t="s">
         <v>149</v>
       </c>
       <c r="B143" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>181</v>
@@ -14768,8 +14844,8 @@
       <c r="W143" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X143" s="1" t="s">
-        <v>103</v>
+      <c r="X143" s="1">
+        <v>2028</v>
       </c>
       <c r="AD143" s="1" t="s">
         <v>104</v>
@@ -14824,12 +14900,12 @@
       </c>
       <c r="AX143" s="2"/>
     </row>
-    <row r="144" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A144" t="s">
         <v>149</v>
       </c>
       <c r="B144" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>181</v>
@@ -14888,8 +14964,8 @@
       <c r="W144" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X144" s="1" t="s">
-        <v>103</v>
+      <c r="X144" s="1">
+        <v>2028</v>
       </c>
       <c r="AD144" s="1" t="s">
         <v>104</v>
@@ -14944,12 +15020,12 @@
       </c>
       <c r="AX144" s="2"/>
     </row>
-    <row r="145" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A145" t="s">
         <v>149</v>
       </c>
       <c r="B145" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>181</v>
@@ -15008,8 +15084,8 @@
       <c r="W145" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X145" s="1" t="s">
-        <v>103</v>
+      <c r="X145" s="1">
+        <v>2028</v>
       </c>
       <c r="AD145" s="1" t="s">
         <v>104</v>
@@ -15064,12 +15140,12 @@
       </c>
       <c r="AX145" s="2"/>
     </row>
-    <row r="146" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A146" t="s">
         <v>149</v>
       </c>
       <c r="B146" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>181</v>
@@ -15128,8 +15204,8 @@
       <c r="W146" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X146" s="1" t="s">
-        <v>103</v>
+      <c r="X146" s="1">
+        <v>2028</v>
       </c>
       <c r="AD146" s="1" t="s">
         <v>104</v>
@@ -15184,12 +15260,12 @@
       </c>
       <c r="AX146" s="2"/>
     </row>
-    <row r="147" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A147" t="s">
         <v>149</v>
       </c>
       <c r="B147" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>181</v>
@@ -15248,8 +15324,8 @@
       <c r="W147" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X147" s="1" t="s">
-        <v>103</v>
+      <c r="X147" s="1">
+        <v>2028</v>
       </c>
       <c r="AD147" s="1" t="s">
         <v>104</v>
@@ -15304,12 +15380,12 @@
       </c>
       <c r="AX147" s="2"/>
     </row>
-    <row r="148" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A148" t="s">
         <v>149</v>
       </c>
       <c r="B148" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>181</v>
@@ -15368,8 +15444,8 @@
       <c r="W148" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X148" s="1" t="s">
-        <v>103</v>
+      <c r="X148" s="1">
+        <v>2028</v>
       </c>
       <c r="AD148" s="1" t="s">
         <v>104</v>
@@ -15424,12 +15500,12 @@
       </c>
       <c r="AX148" s="2"/>
     </row>
-    <row r="149" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A149" t="s">
         <v>149</v>
       </c>
       <c r="B149" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>181</v>
@@ -15488,8 +15564,8 @@
       <c r="W149" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X149" s="1" t="s">
-        <v>103</v>
+      <c r="X149" s="1">
+        <v>2028</v>
       </c>
       <c r="AD149" s="1" t="s">
         <v>104</v>
@@ -15544,12 +15620,12 @@
       </c>
       <c r="AX149" s="2"/>
     </row>
-    <row r="150" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A150" t="s">
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>181</v>
@@ -15608,8 +15684,8 @@
       <c r="W150" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X150" s="1" t="s">
-        <v>103</v>
+      <c r="X150" s="1">
+        <v>2028</v>
       </c>
       <c r="AD150" s="1" t="s">
         <v>104</v>
@@ -15664,12 +15740,12 @@
       </c>
       <c r="AX150" s="2"/>
     </row>
-    <row r="151" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A151" t="s">
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>181</v>
@@ -15728,8 +15804,8 @@
       <c r="W151" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X151" s="1" t="s">
-        <v>103</v>
+      <c r="X151" s="1">
+        <v>2028</v>
       </c>
       <c r="AD151" s="1" t="s">
         <v>104</v>
@@ -15784,12 +15860,12 @@
       </c>
       <c r="AX151" s="2"/>
     </row>
-    <row r="152" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A152" t="s">
         <v>149</v>
       </c>
       <c r="B152" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>185</v>
@@ -15848,8 +15924,8 @@
       <c r="W152" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X152" s="1" t="s">
-        <v>103</v>
+      <c r="X152" s="1">
+        <v>2028</v>
       </c>
       <c r="AD152" s="1" t="s">
         <v>104</v>
@@ -15904,12 +15980,12 @@
       </c>
       <c r="AX152" s="2"/>
     </row>
-    <row r="153" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A153" t="s">
         <v>149</v>
       </c>
       <c r="B153" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>185</v>
@@ -15968,8 +16044,8 @@
       <c r="W153" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X153" s="1" t="s">
-        <v>103</v>
+      <c r="X153" s="1">
+        <v>2028</v>
       </c>
       <c r="AD153" s="1" t="s">
         <v>104</v>
@@ -16024,12 +16100,12 @@
       </c>
       <c r="AX153" s="2"/>
     </row>
-    <row r="154" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A154" t="s">
         <v>149</v>
       </c>
       <c r="B154" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>185</v>
@@ -16088,8 +16164,8 @@
       <c r="W154" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X154" s="1" t="s">
-        <v>103</v>
+      <c r="X154" s="1">
+        <v>2028</v>
       </c>
       <c r="AD154" s="1" t="s">
         <v>104</v>
@@ -16144,12 +16220,12 @@
       </c>
       <c r="AX154" s="2"/>
     </row>
-    <row r="155" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A155" t="s">
         <v>149</v>
       </c>
       <c r="B155" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>185</v>
@@ -16208,8 +16284,8 @@
       <c r="W155" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X155" s="1" t="s">
-        <v>103</v>
+      <c r="X155" s="1">
+        <v>2028</v>
       </c>
       <c r="AD155" s="1" t="s">
         <v>104</v>
@@ -16264,12 +16340,12 @@
       </c>
       <c r="AX155" s="2"/>
     </row>
-    <row r="156" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A156" t="s">
         <v>149</v>
       </c>
       <c r="B156" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>185</v>
@@ -16328,8 +16404,8 @@
       <c r="W156" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X156" s="1" t="s">
-        <v>103</v>
+      <c r="X156" s="1">
+        <v>2028</v>
       </c>
       <c r="AD156" s="1" t="s">
         <v>104</v>
@@ -16384,12 +16460,12 @@
       </c>
       <c r="AX156" s="2"/>
     </row>
-    <row r="157" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A157" t="s">
         <v>149</v>
       </c>
       <c r="B157" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>185</v>
@@ -16448,8 +16524,8 @@
       <c r="W157" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X157" s="1" t="s">
-        <v>103</v>
+      <c r="X157" s="1">
+        <v>2028</v>
       </c>
       <c r="AD157" s="1" t="s">
         <v>104</v>
@@ -16504,12 +16580,12 @@
       </c>
       <c r="AX157" s="2"/>
     </row>
-    <row r="158" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A158" t="s">
         <v>149</v>
       </c>
       <c r="B158" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>185</v>
@@ -16568,8 +16644,8 @@
       <c r="W158" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X158" s="1" t="s">
-        <v>103</v>
+      <c r="X158" s="1">
+        <v>2028</v>
       </c>
       <c r="AD158" s="1" t="s">
         <v>104</v>
@@ -16624,12 +16700,12 @@
       </c>
       <c r="AX158" s="2"/>
     </row>
-    <row r="159" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A159" t="s">
         <v>149</v>
       </c>
       <c r="B159" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>185</v>
@@ -16688,8 +16764,8 @@
       <c r="W159" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X159" s="1" t="s">
-        <v>103</v>
+      <c r="X159" s="1">
+        <v>2028</v>
       </c>
       <c r="AD159" s="1" t="s">
         <v>104</v>
@@ -16744,12 +16820,12 @@
       </c>
       <c r="AX159" s="2"/>
     </row>
-    <row r="160" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A160" t="s">
         <v>149</v>
       </c>
       <c r="B160" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>185</v>
@@ -16808,8 +16884,8 @@
       <c r="W160" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X160" s="1" t="s">
-        <v>103</v>
+      <c r="X160" s="1">
+        <v>2028</v>
       </c>
       <c r="AD160" s="1" t="s">
         <v>104</v>
@@ -16864,12 +16940,12 @@
       </c>
       <c r="AX160" s="2"/>
     </row>
-    <row r="161" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A161" t="s">
         <v>149</v>
       </c>
       <c r="B161" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>185</v>
@@ -16928,8 +17004,8 @@
       <c r="W161" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X161" s="1" t="s">
-        <v>103</v>
+      <c r="X161" s="1">
+        <v>2028</v>
       </c>
       <c r="AD161" s="1" t="s">
         <v>104</v>
@@ -16984,12 +17060,12 @@
       </c>
       <c r="AX161" s="2"/>
     </row>
-    <row r="162" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A162" t="s">
         <v>149</v>
       </c>
       <c r="B162" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>185</v>
@@ -17048,8 +17124,8 @@
       <c r="W162" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X162" s="1" t="s">
-        <v>103</v>
+      <c r="X162" s="1">
+        <v>2028</v>
       </c>
       <c r="AD162" s="1" t="s">
         <v>104</v>
@@ -17104,12 +17180,12 @@
       </c>
       <c r="AX162" s="2"/>
     </row>
-    <row r="163" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A163" t="s">
         <v>149</v>
       </c>
       <c r="B163" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>185</v>
@@ -17168,8 +17244,8 @@
       <c r="W163" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X163" s="1" t="s">
-        <v>103</v>
+      <c r="X163" s="1">
+        <v>2028</v>
       </c>
       <c r="AD163" s="1" t="s">
         <v>104</v>
@@ -17224,12 +17300,12 @@
       </c>
       <c r="AX163" s="2"/>
     </row>
-    <row r="164" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A164" t="s">
         <v>149</v>
       </c>
       <c r="B164" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>187</v>
@@ -17288,8 +17364,8 @@
       <c r="W164" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X164" s="1" t="s">
-        <v>103</v>
+      <c r="X164" s="1">
+        <v>2028</v>
       </c>
       <c r="AD164" s="1" t="s">
         <v>104</v>
@@ -17344,12 +17420,12 @@
       </c>
       <c r="AX164" s="2"/>
     </row>
-    <row r="165" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A165" t="s">
         <v>149</v>
       </c>
       <c r="B165" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>187</v>
@@ -17408,8 +17484,8 @@
       <c r="W165" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X165" s="1" t="s">
-        <v>103</v>
+      <c r="X165" s="1">
+        <v>2028</v>
       </c>
       <c r="AD165" s="1" t="s">
         <v>104</v>
@@ -17464,12 +17540,12 @@
       </c>
       <c r="AX165" s="2"/>
     </row>
-    <row r="166" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A166" t="s">
         <v>149</v>
       </c>
       <c r="B166" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>187</v>
@@ -17528,8 +17604,8 @@
       <c r="W166" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X166" s="1" t="s">
-        <v>103</v>
+      <c r="X166" s="1">
+        <v>2028</v>
       </c>
       <c r="AD166" s="1" t="s">
         <v>104</v>
@@ -17584,12 +17660,12 @@
       </c>
       <c r="AX166" s="2"/>
     </row>
-    <row r="167" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A167" t="s">
         <v>150</v>
       </c>
       <c r="B167" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>187</v>
@@ -17648,8 +17724,8 @@
       <c r="W167" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X167" s="1" t="s">
-        <v>103</v>
+      <c r="X167" s="1">
+        <v>2028</v>
       </c>
       <c r="AD167" s="1" t="s">
         <v>104</v>
@@ -17704,12 +17780,12 @@
       </c>
       <c r="AX167" s="2"/>
     </row>
-    <row r="168" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A168" t="s">
         <v>150</v>
       </c>
       <c r="B168" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>187</v>
@@ -17768,8 +17844,8 @@
       <c r="W168" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X168" s="1" t="s">
-        <v>103</v>
+      <c r="X168" s="1">
+        <v>2028</v>
       </c>
       <c r="AD168" s="1" t="s">
         <v>104</v>
@@ -17824,12 +17900,12 @@
       </c>
       <c r="AX168" s="2"/>
     </row>
-    <row r="169" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A169" t="s">
         <v>150</v>
       </c>
       <c r="B169" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>187</v>
@@ -17888,8 +17964,8 @@
       <c r="W169" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X169" s="1" t="s">
-        <v>103</v>
+      <c r="X169" s="1">
+        <v>2028</v>
       </c>
       <c r="AD169" s="1" t="s">
         <v>104</v>
@@ -17944,12 +18020,12 @@
       </c>
       <c r="AX169" s="2"/>
     </row>
-    <row r="170" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A170" t="s">
         <v>149</v>
       </c>
       <c r="B170" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>187</v>
@@ -18008,8 +18084,8 @@
       <c r="W170" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X170" s="1" t="s">
-        <v>103</v>
+      <c r="X170" s="1">
+        <v>2028</v>
       </c>
       <c r="AD170" s="1" t="s">
         <v>104</v>
@@ -18064,12 +18140,12 @@
       </c>
       <c r="AX170" s="2"/>
     </row>
-    <row r="171" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A171" t="s">
         <v>149</v>
       </c>
       <c r="B171" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>187</v>
@@ -18128,8 +18204,8 @@
       <c r="W171" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X171" s="1" t="s">
-        <v>103</v>
+      <c r="X171" s="1">
+        <v>2028</v>
       </c>
       <c r="AD171" s="1" t="s">
         <v>104</v>
@@ -18184,12 +18260,12 @@
       </c>
       <c r="AX171" s="2"/>
     </row>
-    <row r="172" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A172" t="s">
         <v>149</v>
       </c>
       <c r="B172" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>187</v>
@@ -18248,8 +18324,8 @@
       <c r="W172" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X172" s="1" t="s">
-        <v>103</v>
+      <c r="X172" s="1">
+        <v>2028</v>
       </c>
       <c r="AD172" s="1" t="s">
         <v>104</v>
@@ -18304,12 +18380,12 @@
       </c>
       <c r="AX172" s="2"/>
     </row>
-    <row r="173" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A173" t="s">
         <v>149</v>
       </c>
       <c r="B173" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>187</v>
@@ -18368,8 +18444,8 @@
       <c r="W173" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X173" s="1" t="s">
-        <v>103</v>
+      <c r="X173" s="1">
+        <v>2028</v>
       </c>
       <c r="AD173" s="1" t="s">
         <v>104</v>
@@ -18424,12 +18500,12 @@
       </c>
       <c r="AX173" s="2"/>
     </row>
-    <row r="174" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A174" t="s">
         <v>149</v>
       </c>
       <c r="B174" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>187</v>
@@ -18488,8 +18564,8 @@
       <c r="W174" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X174" s="1" t="s">
-        <v>103</v>
+      <c r="X174" s="1">
+        <v>2028</v>
       </c>
       <c r="AD174" s="1" t="s">
         <v>104</v>
@@ -18544,12 +18620,12 @@
       </c>
       <c r="AX174" s="2"/>
     </row>
-    <row r="175" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A175" t="s">
         <v>149</v>
       </c>
       <c r="B175" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>187</v>
@@ -18608,8 +18684,8 @@
       <c r="W175" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X175" s="1" t="s">
-        <v>103</v>
+      <c r="X175" s="1">
+        <v>2028</v>
       </c>
       <c r="AD175" s="1" t="s">
         <v>104</v>
@@ -18667,8 +18743,8 @@
   </sheetData>
   <autoFilter ref="G1:G175" xr:uid="{01D907F6-7637-41F5-9F0A-BDDAA86240AA}"/>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup horizontalDpi="4294967293" orientation="portrait" r:id="rId1" verticalDpi="0"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>
@@ -18676,68 +18752,68 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E373AFE3-95E6-4012-963C-FB304E9ADB66}">
-  <dimension ref="A1:AW115"/>
-  <sheetFormatPr defaultColWidth="26.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E373AFE3-95E6-4012-963C-FB304E9ADB66}">
+  <dimension ref="A1:AX115"/>
+  <sheetFormatPr defaultColWidth="26.73046875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.1796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="26.7265625" style="1" collapsed="1"/>
-    <col min="3" max="3" width="32" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="9.1796875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="4.7265625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="6.453125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="10" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="9.453125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="11.7265625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="8.81640625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="6.7265625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="12" max="12" width="13.7265625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="13" max="13" width="19.1796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="14" max="14" width="22.26953125" style="1" customWidth="1" collapsed="1"/>
-    <col min="15" max="15" width="8" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="16" max="16" width="9.26953125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="17" max="17" width="5.54296875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="18" max="18" width="6" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="19" max="19" width="9.81640625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="20" max="20" width="8.1796875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="21" max="21" width="24" style="1" customWidth="1" collapsed="1"/>
-    <col min="22" max="22" width="4.7265625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="23" max="23" width="8.81640625" style="1" customWidth="1" collapsed="1"/>
-    <col min="24" max="24" width="8.7265625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="25" max="25" width="9.26953125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="26" max="26" width="115.453125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="27" max="27" width="75.54296875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="28" max="28" width="40.54296875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="29" max="29" width="14.453125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="30" max="30" width="23.81640625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="31" max="31" width="13.54296875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="32" max="32" width="11.1796875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="33" max="33" width="18" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="34" max="34" width="7" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="35" max="35" width="14.7265625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="36" max="44" width="10.453125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="45" max="45" width="11.453125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="46" max="47" width="13.7265625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="48" max="48" width="12.54296875" style="1" customWidth="1" collapsed="1"/>
-    <col min="49" max="49" width="15" style="1" customWidth="1" collapsed="1"/>
-    <col min="50" max="50" width="14.453125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="51" max="51" width="9.1796875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="52" max="52" width="12" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="53" max="53" width="11.54296875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="54" max="54" width="15.26953125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="55" max="55" width="14.7265625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="56" max="56" width="15.7265625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="57" max="57" width="11.81640625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="58" max="58" width="18.26953125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="59" max="59" width="14.81640625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="60" max="61" width="15.81640625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="62" max="62" width="16.453125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="63" max="63" width="10" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="64" max="64" width="10.7265625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="65" max="16384" width="26.7265625" style="1" collapsed="1"/>
+    <col min="1" max="1" customWidth="true" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" style="1" width="26.73046875" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="32.0" collapsed="true"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="9.19921875" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="4.73046875" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="6.46484375" collapsed="true"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="10.0" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="9.46484375" collapsed="true"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="11.73046875" collapsed="true"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="1" width="8.796875" collapsed="true"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="6.73046875" collapsed="true"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="13.73046875" collapsed="true"/>
+    <col min="13" max="13" customWidth="true" style="1" width="19.19921875" collapsed="true"/>
+    <col min="14" max="14" customWidth="true" style="1" width="22.265625" collapsed="true"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="8.0" collapsed="true"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" style="1" width="9.265625" collapsed="true"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="5.53125" collapsed="true"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="6.0" collapsed="true"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="9.796875" collapsed="true"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="8.19921875" collapsed="true"/>
+    <col min="21" max="21" customWidth="true" style="1" width="24.0" collapsed="true"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="4.73046875" collapsed="true"/>
+    <col min="23" max="23" customWidth="true" style="1" width="8.796875" collapsed="true"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" style="1" width="8.73046875" collapsed="true"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" style="1" width="9.265625" collapsed="true"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" style="1" width="115.46484375" collapsed="true"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="75.53125" collapsed="true"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="40.53125" collapsed="true"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="14.46484375" collapsed="true"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="23.796875" collapsed="true"/>
+    <col min="31" max="31" bestFit="true" customWidth="true" style="1" width="13.53125" collapsed="true"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="11.19921875" collapsed="true"/>
+    <col min="33" max="33" bestFit="true" customWidth="true" style="1" width="18.0" collapsed="true"/>
+    <col min="34" max="34" bestFit="true" customWidth="true" style="1" width="7.0" collapsed="true"/>
+    <col min="35" max="35" bestFit="true" customWidth="true" style="1" width="14.73046875" collapsed="true"/>
+    <col min="36" max="44" bestFit="true" customWidth="true" style="1" width="10.46484375" collapsed="true"/>
+    <col min="45" max="45" bestFit="true" customWidth="true" style="1" width="11.46484375" collapsed="true"/>
+    <col min="46" max="47" bestFit="true" customWidth="true" style="1" width="13.73046875" collapsed="true"/>
+    <col min="48" max="48" customWidth="true" style="1" width="12.53125" collapsed="true"/>
+    <col min="49" max="49" customWidth="true" style="1" width="15.0" collapsed="true"/>
+    <col min="50" max="50" bestFit="true" customWidth="true" style="1" width="14.46484375" collapsed="true"/>
+    <col min="51" max="51" bestFit="true" customWidth="true" style="1" width="9.19921875" collapsed="true"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" style="1" width="12.0" collapsed="true"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" style="1" width="11.53125" collapsed="true"/>
+    <col min="54" max="54" bestFit="true" customWidth="true" style="1" width="15.265625" collapsed="true"/>
+    <col min="55" max="55" bestFit="true" customWidth="true" style="1" width="14.73046875" collapsed="true"/>
+    <col min="56" max="56" bestFit="true" customWidth="true" style="1" width="15.73046875" collapsed="true"/>
+    <col min="57" max="57" bestFit="true" customWidth="true" style="1" width="11.796875" collapsed="true"/>
+    <col min="58" max="58" bestFit="true" customWidth="true" style="1" width="18.265625" collapsed="true"/>
+    <col min="59" max="59" bestFit="true" customWidth="true" style="1" width="14.796875" collapsed="true"/>
+    <col min="60" max="61" bestFit="true" customWidth="true" style="1" width="15.796875" collapsed="true"/>
+    <col min="62" max="62" bestFit="true" customWidth="true" style="1" width="16.46484375" collapsed="true"/>
+    <col min="63" max="63" bestFit="true" customWidth="true" style="1" width="10.0" collapsed="true"/>
+    <col min="64" max="64" bestFit="true" customWidth="true" style="1" width="10.73046875" collapsed="true"/>
+    <col min="65" max="16384" style="1" width="26.73046875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:49" ht="29" x14ac:dyDescent="0.35">
+    <row ht="28.5" r="1" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>145</v>
       </c>
@@ -18886,7 +18962,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>147</v>
       </c>
@@ -19000,7 +19076,7 @@
       </c>
       <c r="AW2" s="2"/>
     </row>
-    <row r="3" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>147</v>
       </c>
@@ -19061,7 +19137,7 @@
       <c r="AD3" s="2"/>
       <c r="AW3" s="2"/>
     </row>
-    <row r="4" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>147</v>
       </c>
@@ -19122,7 +19198,7 @@
       <c r="AD4" s="2"/>
       <c r="AW4" s="2"/>
     </row>
-    <row r="5" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>147</v>
       </c>
@@ -19236,7 +19312,7 @@
       </c>
       <c r="AW5" s="2"/>
     </row>
-    <row r="6" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
         <v>147</v>
       </c>
@@ -19297,7 +19373,7 @@
       <c r="AD6" s="2"/>
       <c r="AW6" s="2"/>
     </row>
-    <row r="7" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
         <v>147</v>
       </c>
@@ -19358,7 +19434,7 @@
       <c r="AD7" s="2"/>
       <c r="AW7" s="2"/>
     </row>
-    <row r="8" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
         <v>147</v>
       </c>
@@ -19472,7 +19548,7 @@
       </c>
       <c r="AW8" s="2"/>
     </row>
-    <row r="9" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
         <v>147</v>
       </c>
@@ -19533,7 +19609,7 @@
       <c r="AD9" s="2"/>
       <c r="AW9" s="2"/>
     </row>
-    <row r="10" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
         <v>147</v>
       </c>
@@ -19594,7 +19670,7 @@
       <c r="AD10" s="2"/>
       <c r="AW10" s="2"/>
     </row>
-    <row r="11" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
         <v>147</v>
       </c>
@@ -19708,7 +19784,7 @@
       </c>
       <c r="AW11" s="2"/>
     </row>
-    <row r="12" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
         <v>147</v>
       </c>
@@ -19769,7 +19845,7 @@
       <c r="AD12" s="2"/>
       <c r="AW12" s="2"/>
     </row>
-    <row r="13" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
         <v>147</v>
       </c>
@@ -19830,7 +19906,7 @@
       <c r="AD13" s="2"/>
       <c r="AW13" s="2"/>
     </row>
-    <row r="14" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
         <v>147</v>
       </c>
@@ -19944,7 +20020,7 @@
       </c>
       <c r="AW14" s="2"/>
     </row>
-    <row r="15" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
         <v>147</v>
       </c>
@@ -20005,7 +20081,7 @@
       <c r="AD15" s="2"/>
       <c r="AW15" s="2"/>
     </row>
-    <row r="16" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
         <v>147</v>
       </c>
@@ -20066,7 +20142,7 @@
       <c r="AD16" s="2"/>
       <c r="AW16" s="2"/>
     </row>
-    <row r="17" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
         <v>147</v>
       </c>
@@ -20180,7 +20256,7 @@
       </c>
       <c r="AW17" s="2"/>
     </row>
-    <row r="18" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
         <v>147</v>
       </c>
@@ -20241,7 +20317,7 @@
       <c r="AD18" s="2"/>
       <c r="AW18" s="2"/>
     </row>
-    <row r="19" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
         <v>147</v>
       </c>
@@ -20302,7 +20378,7 @@
       <c r="AD19" s="2"/>
       <c r="AW19" s="2"/>
     </row>
-    <row r="20" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="s">
         <v>147</v>
       </c>
@@ -20416,7 +20492,7 @@
       </c>
       <c r="AW20" s="2"/>
     </row>
-    <row r="21" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
         <v>147</v>
       </c>
@@ -20477,7 +20553,7 @@
       <c r="AD21" s="2"/>
       <c r="AW21" s="2"/>
     </row>
-    <row r="22" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
         <v>147</v>
       </c>
@@ -20538,7 +20614,7 @@
       <c r="AD22" s="2"/>
       <c r="AW22" s="2"/>
     </row>
-    <row r="23" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A23" s="1" t="s">
         <v>147</v>
       </c>
@@ -20652,7 +20728,7 @@
       </c>
       <c r="AW23" s="2"/>
     </row>
-    <row r="24" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A24" s="1" t="s">
         <v>147</v>
       </c>
@@ -20713,7 +20789,7 @@
       <c r="AD24" s="2"/>
       <c r="AW24" s="2"/>
     </row>
-    <row r="25" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A25" s="1" t="s">
         <v>147</v>
       </c>
@@ -20774,7 +20850,7 @@
       <c r="AD25" s="2"/>
       <c r="AW25" s="2"/>
     </row>
-    <row r="26" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A26" s="1" t="s">
         <v>147</v>
       </c>
@@ -20888,7 +20964,7 @@
       </c>
       <c r="AW26" s="2"/>
     </row>
-    <row r="27" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A27" s="1" t="s">
         <v>147</v>
       </c>
@@ -20949,7 +21025,7 @@
       <c r="AD27" s="2"/>
       <c r="AW27" s="2"/>
     </row>
-    <row r="28" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A28" s="1" t="s">
         <v>147</v>
       </c>
@@ -21010,7 +21086,7 @@
       <c r="AD28" s="2"/>
       <c r="AW28" s="2"/>
     </row>
-    <row r="29" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A29" s="1" t="s">
         <v>147</v>
       </c>
@@ -21124,7 +21200,7 @@
       </c>
       <c r="AW29" s="2"/>
     </row>
-    <row r="30" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A30" s="1" t="s">
         <v>147</v>
       </c>
@@ -21185,7 +21261,7 @@
       <c r="AD30" s="2"/>
       <c r="AW30" s="2"/>
     </row>
-    <row r="31" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A31" s="1" t="s">
         <v>147</v>
       </c>
@@ -21246,7 +21322,7 @@
       <c r="AD31" s="2"/>
       <c r="AW31" s="2"/>
     </row>
-    <row r="32" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A32" s="1" t="s">
         <v>147</v>
       </c>
@@ -21360,7 +21436,7 @@
       </c>
       <c r="AW32" s="2"/>
     </row>
-    <row r="33" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A33" s="1" t="s">
         <v>147</v>
       </c>
@@ -21421,7 +21497,7 @@
       <c r="AD33" s="2"/>
       <c r="AW33" s="2"/>
     </row>
-    <row r="34" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A34" s="1" t="s">
         <v>147</v>
       </c>
@@ -21482,7 +21558,7 @@
       <c r="AD34" s="2"/>
       <c r="AW34" s="2"/>
     </row>
-    <row r="35" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A35" s="1" t="s">
         <v>147</v>
       </c>
@@ -21596,7 +21672,7 @@
       </c>
       <c r="AW35" s="2"/>
     </row>
-    <row r="36" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A36" s="1" t="s">
         <v>147</v>
       </c>
@@ -21657,7 +21733,7 @@
       <c r="AD36" s="2"/>
       <c r="AW36" s="2"/>
     </row>
-    <row r="37" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A37" s="1" t="s">
         <v>147</v>
       </c>
@@ -21718,7 +21794,7 @@
       <c r="AD37" s="2"/>
       <c r="AW37" s="2"/>
     </row>
-    <row r="38" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A38" s="1" t="s">
         <v>147</v>
       </c>
@@ -21832,7 +21908,7 @@
       </c>
       <c r="AW38" s="2"/>
     </row>
-    <row r="39" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A39" s="1" t="s">
         <v>147</v>
       </c>
@@ -21893,7 +21969,7 @@
       <c r="AD39" s="2"/>
       <c r="AW39" s="2"/>
     </row>
-    <row r="40" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A40" s="1" t="s">
         <v>147</v>
       </c>
@@ -21954,7 +22030,7 @@
       <c r="AD40" s="2"/>
       <c r="AW40" s="2"/>
     </row>
-    <row r="41" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A41" s="1" t="s">
         <v>147</v>
       </c>
@@ -22068,7 +22144,7 @@
       </c>
       <c r="AW41" s="2"/>
     </row>
-    <row r="42" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A42" s="1" t="s">
         <v>147</v>
       </c>
@@ -22129,7 +22205,7 @@
       <c r="AD42" s="2"/>
       <c r="AW42" s="2"/>
     </row>
-    <row r="43" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A43" s="1" t="s">
         <v>147</v>
       </c>
@@ -22190,7 +22266,7 @@
       <c r="AD43" s="2"/>
       <c r="AW43" s="2"/>
     </row>
-    <row r="44" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A44" s="1" t="s">
         <v>147</v>
       </c>
@@ -22304,7 +22380,7 @@
       </c>
       <c r="AW44" s="2"/>
     </row>
-    <row r="45" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A45" s="1" t="s">
         <v>147</v>
       </c>
@@ -22365,7 +22441,7 @@
       <c r="AD45" s="2"/>
       <c r="AW45" s="2"/>
     </row>
-    <row r="46" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A46" s="1" t="s">
         <v>147</v>
       </c>
@@ -22426,7 +22502,7 @@
       <c r="AD46" s="2"/>
       <c r="AW46" s="2"/>
     </row>
-    <row r="47" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A47" s="1" t="s">
         <v>147</v>
       </c>
@@ -22540,7 +22616,7 @@
       </c>
       <c r="AW47" s="2"/>
     </row>
-    <row r="48" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A48" s="1" t="s">
         <v>147</v>
       </c>
@@ -22601,7 +22677,7 @@
       <c r="AD48" s="2"/>
       <c r="AW48" s="2"/>
     </row>
-    <row r="49" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A49" s="1" t="s">
         <v>147</v>
       </c>
@@ -22662,7 +22738,7 @@
       <c r="AD49" s="2"/>
       <c r="AW49" s="2"/>
     </row>
-    <row r="50" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A50" s="1" t="s">
         <v>147</v>
       </c>
@@ -22737,7 +22813,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="51" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A51" s="1" t="s">
         <v>147</v>
       </c>
@@ -22865,7 +22941,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="52" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A52" s="1" t="s">
         <v>147</v>
       </c>
@@ -22940,7 +23016,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="53" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A53" s="1" t="s">
         <v>147</v>
       </c>
@@ -23068,7 +23144,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="54" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A54" s="1" t="s">
         <v>147</v>
       </c>
@@ -23143,7 +23219,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="55" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A55" s="1" t="s">
         <v>147</v>
       </c>
@@ -23271,7 +23347,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="56" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A56" s="1" t="s">
         <v>147</v>
       </c>
@@ -23346,7 +23422,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="57" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A57" s="1" t="s">
         <v>147</v>
       </c>
@@ -23474,7 +23550,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="58" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A58" s="1" t="s">
         <v>147</v>
       </c>
@@ -23549,7 +23625,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="59" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A59" s="1" t="s">
         <v>147</v>
       </c>
@@ -23677,7 +23753,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="60" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A60" s="1" t="s">
         <v>147</v>
       </c>
@@ -23752,7 +23828,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="61" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A61" s="1" t="s">
         <v>147</v>
       </c>
@@ -23880,7 +23956,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="62" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A62" s="1" t="s">
         <v>147</v>
       </c>
@@ -24008,7 +24084,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="63" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A63" s="1" t="s">
         <v>147</v>
       </c>
@@ -24083,7 +24159,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="64" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A64" s="1" t="s">
         <v>147</v>
       </c>
@@ -24158,7 +24234,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="65" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A65" s="1" t="s">
         <v>147</v>
       </c>
@@ -24286,7 +24362,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="66" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A66" s="1" t="s">
         <v>147</v>
       </c>
@@ -24361,7 +24437,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="67" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A67" s="1" t="s">
         <v>147</v>
       </c>
@@ -24436,7 +24512,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="68" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A68" s="1" t="s">
         <v>147</v>
       </c>
@@ -24564,7 +24640,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="69" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A69" s="1" t="s">
         <v>147</v>
       </c>
@@ -24639,7 +24715,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="70" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A70" s="1" t="s">
         <v>147</v>
       </c>
@@ -24714,7 +24790,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="71" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A71" s="1" t="s">
         <v>147</v>
       </c>
@@ -24842,7 +24918,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="72" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A72" s="1" t="s">
         <v>147</v>
       </c>
@@ -24917,7 +24993,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="73" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A73" s="1" t="s">
         <v>147</v>
       </c>
@@ -24992,7 +25068,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="74" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A74" s="1" t="s">
         <v>147</v>
       </c>
@@ -25067,7 +25143,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="75" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A75" s="1" t="s">
         <v>147</v>
       </c>
@@ -25195,7 +25271,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="76" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A76" s="1" t="s">
         <v>147</v>
       </c>
@@ -25270,7 +25346,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="77" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A77" s="1" t="s">
         <v>147</v>
       </c>
@@ -25398,7 +25474,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="78" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A78" s="1" t="s">
         <v>147</v>
       </c>
@@ -25473,7 +25549,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="79" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A79" s="1" t="s">
         <v>147</v>
       </c>
@@ -25601,7 +25677,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="80" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A80" s="1" t="s">
         <v>147</v>
       </c>
@@ -25676,7 +25752,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="81" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A81" s="1" t="s">
         <v>147</v>
       </c>
@@ -25804,7 +25880,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="82" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A82" s="1" t="s">
         <v>147</v>
       </c>
@@ -25879,7 +25955,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="83" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A83" s="1" t="s">
         <v>147</v>
       </c>
@@ -26007,7 +26083,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="84" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A84" s="1" t="s">
         <v>147</v>
       </c>
@@ -26082,7 +26158,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="85" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A85" s="1" t="s">
         <v>147</v>
       </c>
@@ -26210,7 +26286,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="86" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A86" s="1" t="s">
         <v>147</v>
       </c>
@@ -26338,7 +26414,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="87" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A87" s="1" t="s">
         <v>147</v>
       </c>
@@ -26413,7 +26489,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="88" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A88" s="1" t="s">
         <v>147</v>
       </c>
@@ -26488,7 +26564,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="89" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A89" s="1" t="s">
         <v>147</v>
       </c>
@@ -26616,7 +26692,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="90" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A90" s="1" t="s">
         <v>147</v>
       </c>
@@ -26691,7 +26767,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="91" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A91" s="1" t="s">
         <v>147</v>
       </c>
@@ -26766,7 +26842,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="92" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A92" s="1" t="s">
         <v>147</v>
       </c>
@@ -26894,7 +26970,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="93" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A93" s="1" t="s">
         <v>147</v>
       </c>
@@ -26969,7 +27045,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="94" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A94" s="1" t="s">
         <v>147</v>
       </c>
@@ -27044,7 +27120,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="95" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A95" s="1" t="s">
         <v>147</v>
       </c>
@@ -27172,7 +27248,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="96" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A96" s="1" t="s">
         <v>147</v>
       </c>
@@ -27247,7 +27323,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="97" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A97" s="1" t="s">
         <v>147</v>
       </c>
@@ -27322,7 +27398,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="98" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A98" s="1" t="s">
         <v>147</v>
       </c>
@@ -27377,7 +27453,7 @@
       <c r="AD98" s="2"/>
       <c r="AW98" s="2"/>
     </row>
-    <row r="99" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A99" s="1" t="s">
         <v>147</v>
       </c>
@@ -27432,7 +27508,7 @@
       <c r="AD99" s="2"/>
       <c r="AW99" s="2"/>
     </row>
-    <row r="100" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A100" s="1" t="s">
         <v>147</v>
       </c>
@@ -27487,7 +27563,7 @@
       <c r="AD100" s="2"/>
       <c r="AW100" s="2"/>
     </row>
-    <row r="101" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A101" s="1" t="s">
         <v>147</v>
       </c>
@@ -27542,7 +27618,7 @@
       <c r="AD101" s="2"/>
       <c r="AW101" s="2"/>
     </row>
-    <row r="102" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A102" s="1" t="s">
         <v>147</v>
       </c>
@@ -27597,7 +27673,7 @@
       <c r="AD102" s="2"/>
       <c r="AW102" s="2"/>
     </row>
-    <row r="103" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A103" s="1" t="s">
         <v>147</v>
       </c>
@@ -27652,7 +27728,7 @@
       <c r="AD103" s="2"/>
       <c r="AW103" s="2"/>
     </row>
-    <row r="104" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A104" s="1" t="s">
         <v>147</v>
       </c>
@@ -27692,7 +27768,7 @@
       <c r="AD104" s="2"/>
       <c r="AW104" s="2"/>
     </row>
-    <row r="105" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A105" s="1" t="s">
         <v>147</v>
       </c>
@@ -27732,7 +27808,7 @@
       <c r="AD105" s="2"/>
       <c r="AW105" s="2"/>
     </row>
-    <row r="106" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A106" s="1" t="s">
         <v>147</v>
       </c>
@@ -27775,7 +27851,7 @@
       <c r="AD106" s="2"/>
       <c r="AW106" s="2"/>
     </row>
-    <row r="107" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A107" s="1" t="s">
         <v>147</v>
       </c>
@@ -27818,7 +27894,7 @@
       <c r="AD107" s="2"/>
       <c r="AW107" s="2"/>
     </row>
-    <row r="108" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A108" s="1" t="s">
         <v>147</v>
       </c>
@@ -27858,7 +27934,7 @@
       <c r="AD108" s="2"/>
       <c r="AW108" s="2"/>
     </row>
-    <row r="109" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A109" s="1" t="s">
         <v>147</v>
       </c>
@@ -27898,7 +27974,7 @@
       <c r="AD109" s="2"/>
       <c r="AW109" s="2"/>
     </row>
-    <row r="110" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A110" s="1" t="s">
         <v>147</v>
       </c>
@@ -27941,7 +28017,7 @@
       <c r="AD110" s="2"/>
       <c r="AW110" s="2"/>
     </row>
-    <row r="111" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A111" s="1" t="s">
         <v>147</v>
       </c>
@@ -27984,7 +28060,7 @@
       <c r="AD111" s="2"/>
       <c r="AW111" s="2"/>
     </row>
-    <row r="112" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A112" s="1" t="s">
         <v>147</v>
       </c>
@@ -28024,7 +28100,7 @@
       <c r="AD112" s="2"/>
       <c r="AW112" s="2"/>
     </row>
-    <row r="113" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A113" s="1" t="s">
         <v>147</v>
       </c>
@@ -28064,7 +28140,7 @@
       <c r="AD113" s="2"/>
       <c r="AW113" s="2"/>
     </row>
-    <row r="114" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A114" s="1" t="s">
         <v>147</v>
       </c>
@@ -28107,7 +28183,7 @@
       <c r="AD114" s="2"/>
       <c r="AW114" s="2"/>
     </row>
-    <row r="115" spans="1:49" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:49" x14ac:dyDescent="0.45">
       <c r="A115" s="1" t="s">
         <v>147</v>
       </c>
@@ -28151,7 +28227,7 @@
       <c r="AW115" s="2"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>
@@ -28159,14 +28235,14 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97E51003-E6AF-4A46-8DE2-C02177084CDE}">
-  <dimension ref="A1:BS1"/>
-  <sheetFormatPr defaultColWidth="20.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97E51003-E6AF-4A46-8DE2-C02177084CDE}">
+  <dimension ref="A1:BT1"/>
+  <sheetFormatPr defaultColWidth="20.46484375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="16384" width="20.453125" style="1" collapsed="1"/>
+    <col min="1" max="16384" style="1" width="20.46484375" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:71" ht="29" x14ac:dyDescent="0.35">
+    <row ht="28.5" r="1" spans="1:71" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -28382,8 +28458,8 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup horizontalDpi="4294967293" orientation="portrait" r:id="rId1" verticalDpi="0"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>

--- a/KatalonData/VLinkCCTestData.xlsx
+++ b/KatalonData/VLinkCCTestData.xlsx
@@ -1,28 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{BC086086-A28B-4DB9-846E-AA23A341CF6D}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8768CA86-039E-46CA-9A2E-0A1C1FEC0586}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="15675" windowWidth="28996" xWindow="-98" xr2:uid="{8C2F89C9-A10B-4559-913F-0962936A94D9}" yWindow="-98"/>
+    <workbookView xWindow="48288" yWindow="5088" windowWidth="21600" windowHeight="11328" xr2:uid="{8C2F89C9-A10B-4559-913F-0962936A94D9}"/>
   </bookViews>
   <sheets>
-    <sheet name="CCSaleData" r:id="rId1" sheetId="1"/>
-    <sheet name="Trial" r:id="rId2" sheetId="4"/>
-    <sheet name="AuthAndCaptureData" r:id="rId3" sheetId="3"/>
+    <sheet name="CCSaleData" sheetId="1" r:id="rId1"/>
+    <sheet name="Trial" sheetId="4" r:id="rId2"/>
+    <sheet name="AuthAndCaptureData" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">CCSaleData!$G$1:$G$175</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CCSaleData!$G$1:$G$175</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8534" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8438" uniqueCount="362">
   <si>
     <t>Notes</t>
   </si>
@@ -613,75 +613,6 @@
     <t>pwd501</t>
   </si>
   <si>
-    <t>Thu Aug 14 17:33:28 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 14 17:33:40 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 14 17:33:52 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 14 17:34:04 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 14 17:34:14 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 14 17:34:23 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 14 17:34:33 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 14 17:34:42 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 14 17:34:54 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 14 17:35:06 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 14 17:35:15 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 14 17:35:27 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 14 17:35:39 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 14 17:35:51 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 14 17:36:00 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 14 17:36:12 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 14 17:36:23 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 14 17:36:35 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 14 17:36:48 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 14 17:37:00 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 14 17:37:11 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 14 17:37:23 EDT 2025</t>
-  </si>
-  <si>
-    <t>Thu Aug 14 17:37:35 EDT 2025</t>
-  </si>
-  <si>
     <t>Thu Aug 14 17:37:47 EDT 2025</t>
   </si>
   <si>
@@ -1121,12 +1052,6 @@
   </si>
   <si>
     <t>Req Fields Only FDMS Rapid Connect</t>
-  </si>
-  <si>
-    <t>Sat Feb 14 11:52:57 EST 2026</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>Sat Feb 14 11:55:06 EST 2026</t>
@@ -1205,7 +1130,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1254,21 +1178,21 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0"/>
-    <xf applyBorder="1" borderId="1" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1285,10 +1209,10 @@
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -1323,7 +1247,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
-        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -1375,7 +1299,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -1486,21 +1410,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -1517,7 +1441,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -1569,76 +1493,76 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office 2013 - 2022 Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01D907F6-7637-41F5-9F0A-BDDAA86240AA}">
-  <dimension ref="A1:AY175"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01D907F6-7637-41F5-9F0A-BDDAA86240AA}">
+  <dimension ref="A1:AX175"/>
   <sheetFormatPr defaultColWidth="26.73046875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" style="1" width="26.73046875" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="36.0" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="32.0" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="9.19921875" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="4.73046875" collapsed="true"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="6.46484375" collapsed="true"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.0" collapsed="true"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="9.46484375" collapsed="true"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" style="1" width="11.73046875" collapsed="true"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="8.796875" collapsed="true"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="6.73046875" collapsed="true"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="13.73046875" collapsed="true"/>
-    <col min="14" max="14" customWidth="true" style="1" width="19.19921875" collapsed="true"/>
-    <col min="15" max="15" customWidth="true" style="1" width="22.265625" collapsed="true"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" style="1" width="8.0" collapsed="true"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.265625" collapsed="true"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="5.53125" collapsed="true"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="6.0" collapsed="true"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="9.796875" collapsed="true"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="8.19921875" collapsed="true"/>
-    <col min="22" max="22" customWidth="true" style="1" width="24.0" collapsed="true"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="4.73046875" collapsed="true"/>
-    <col min="24" max="24" customWidth="true" style="1" width="8.796875" collapsed="true"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" style="1" width="8.73046875" collapsed="true"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" style="1" width="9.265625" collapsed="true"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="115.46484375" collapsed="true"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="75.53125" collapsed="true"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="40.53125" collapsed="true"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="14.46484375" collapsed="true"/>
-    <col min="31" max="31" bestFit="true" customWidth="true" style="1" width="23.796875" collapsed="true"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="13.53125" collapsed="true"/>
-    <col min="33" max="33" bestFit="true" customWidth="true" style="1" width="11.19921875" collapsed="true"/>
-    <col min="34" max="34" bestFit="true" customWidth="true" style="1" width="18.0" collapsed="true"/>
-    <col min="35" max="35" bestFit="true" customWidth="true" style="1" width="7.0" collapsed="true"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" style="1" width="14.73046875" collapsed="true"/>
-    <col min="37" max="45" bestFit="true" customWidth="true" style="1" width="10.46484375" collapsed="true"/>
-    <col min="46" max="46" bestFit="true" customWidth="true" style="1" width="11.46484375" collapsed="true"/>
-    <col min="47" max="48" bestFit="true" customWidth="true" style="1" width="13.73046875" collapsed="true"/>
-    <col min="49" max="49" customWidth="true" style="1" width="12.53125" collapsed="true"/>
-    <col min="50" max="50" customWidth="true" style="1" width="15.0" collapsed="true"/>
-    <col min="51" max="51" bestFit="true" customWidth="true" style="1" width="14.46484375" collapsed="true"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" style="1" width="9.19921875" collapsed="true"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" style="1" width="12.0" collapsed="true"/>
-    <col min="54" max="54" bestFit="true" customWidth="true" style="1" width="11.53125" collapsed="true"/>
-    <col min="55" max="55" bestFit="true" customWidth="true" style="1" width="15.265625" collapsed="true"/>
-    <col min="56" max="56" bestFit="true" customWidth="true" style="1" width="14.73046875" collapsed="true"/>
-    <col min="57" max="57" bestFit="true" customWidth="true" style="1" width="15.73046875" collapsed="true"/>
-    <col min="58" max="58" bestFit="true" customWidth="true" style="1" width="11.796875" collapsed="true"/>
-    <col min="59" max="59" bestFit="true" customWidth="true" style="1" width="18.265625" collapsed="true"/>
-    <col min="60" max="60" bestFit="true" customWidth="true" style="1" width="14.796875" collapsed="true"/>
-    <col min="61" max="62" bestFit="true" customWidth="true" style="1" width="15.796875" collapsed="true"/>
-    <col min="63" max="63" bestFit="true" customWidth="true" style="1" width="16.46484375" collapsed="true"/>
-    <col min="64" max="64" bestFit="true" customWidth="true" style="1" width="10.0" collapsed="true"/>
-    <col min="65" max="65" bestFit="true" customWidth="true" style="1" width="10.73046875" collapsed="true"/>
-    <col min="66" max="16384" style="1" width="26.73046875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="26.73046875" style="1" collapsed="1"/>
+    <col min="3" max="3" width="36" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="32" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="9.19921875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="4.73046875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="6.46484375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="10" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="9.46484375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="11.73046875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="8.796875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="12" max="12" width="6.73046875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="13" max="13" width="13.73046875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="14" max="14" width="19.19921875" style="1" customWidth="1" collapsed="1"/>
+    <col min="15" max="15" width="22.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="16" max="16" width="8" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="17" max="17" width="9.265625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="18" max="18" width="5.53125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="19" max="19" width="6" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="20" max="20" width="9.796875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="21" max="21" width="8.19921875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="22" max="22" width="24" style="1" customWidth="1" collapsed="1"/>
+    <col min="23" max="23" width="4.73046875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="24" max="24" width="8.796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="25" max="25" width="8.73046875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="26" max="26" width="9.265625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="27" max="27" width="115.46484375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="28" max="28" width="75.53125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="29" max="29" width="40.53125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="30" max="30" width="14.46484375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="31" max="31" width="23.796875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="32" max="32" width="13.53125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="33" max="33" width="11.19921875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="34" max="34" width="18" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="35" max="35" width="7" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="36" max="36" width="14.73046875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="37" max="45" width="10.46484375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="46" max="46" width="11.46484375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="47" max="48" width="13.73046875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="49" max="49" width="12.53125" style="1" customWidth="1" collapsed="1"/>
+    <col min="50" max="50" width="15" style="1" customWidth="1" collapsed="1"/>
+    <col min="51" max="51" width="14.46484375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="52" max="52" width="9.19921875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="53" max="53" width="12" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="54" max="54" width="11.53125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="55" max="55" width="15.265625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="56" max="56" width="14.73046875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="57" max="57" width="15.73046875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="58" max="58" width="11.796875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="59" max="59" width="18.265625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="60" max="60" width="14.796875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="61" max="62" width="15.796875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="63" max="63" width="16.46484375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="64" max="64" width="10" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="65" max="65" width="10.73046875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="66" max="16384" width="26.73046875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row ht="28.5" r="1" spans="1:50" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:50" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>145</v>
       </c>
@@ -1795,7 +1719,7 @@
         <v>150</v>
       </c>
       <c r="B2" t="s">
-        <v>363</v>
+        <v>338</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>153</v>
@@ -1915,7 +1839,7 @@
         <v>150</v>
       </c>
       <c r="B3" t="s">
-        <v>364</v>
+        <v>339</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>153</v>
@@ -1982,7 +1906,7 @@
         <v>150</v>
       </c>
       <c r="B4" t="s">
-        <v>365</v>
+        <v>340</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>153</v>
@@ -2049,7 +1973,7 @@
         <v>150</v>
       </c>
       <c r="B5" t="s">
-        <v>366</v>
+        <v>341</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>153</v>
@@ -2169,7 +2093,7 @@
         <v>150</v>
       </c>
       <c r="B6" t="s">
-        <v>367</v>
+        <v>342</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>153</v>
@@ -2236,7 +2160,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="s">
-        <v>368</v>
+        <v>343</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>153</v>
@@ -2303,7 +2227,7 @@
         <v>150</v>
       </c>
       <c r="B8" t="s">
-        <v>369</v>
+        <v>344</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>153</v>
@@ -2423,7 +2347,7 @@
         <v>150</v>
       </c>
       <c r="B9" t="s">
-        <v>370</v>
+        <v>345</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>153</v>
@@ -2490,7 +2414,7 @@
         <v>150</v>
       </c>
       <c r="B10" t="s">
-        <v>371</v>
+        <v>346</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>153</v>
@@ -2557,7 +2481,7 @@
         <v>150</v>
       </c>
       <c r="B11" t="s">
-        <v>372</v>
+        <v>347</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>153</v>
@@ -2677,7 +2601,7 @@
         <v>150</v>
       </c>
       <c r="B12" t="s">
-        <v>373</v>
+        <v>348</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>153</v>
@@ -2744,7 +2668,7 @@
         <v>150</v>
       </c>
       <c r="B13" t="s">
-        <v>374</v>
+        <v>349</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>153</v>
@@ -2811,7 +2735,7 @@
         <v>150</v>
       </c>
       <c r="B14" t="s">
-        <v>375</v>
+        <v>350</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>153</v>
@@ -2931,7 +2855,7 @@
         <v>150</v>
       </c>
       <c r="B15" t="s">
-        <v>376</v>
+        <v>351</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>153</v>
@@ -2998,7 +2922,7 @@
         <v>150</v>
       </c>
       <c r="B16" t="s">
-        <v>377</v>
+        <v>352</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>153</v>
@@ -3065,7 +2989,7 @@
         <v>150</v>
       </c>
       <c r="B17" t="s">
-        <v>378</v>
+        <v>353</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>153</v>
@@ -3185,7 +3109,7 @@
         <v>150</v>
       </c>
       <c r="B18" t="s">
-        <v>379</v>
+        <v>354</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>153</v>
@@ -3252,7 +3176,7 @@
         <v>150</v>
       </c>
       <c r="B19" t="s">
-        <v>380</v>
+        <v>355</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>153</v>
@@ -3319,7 +3243,7 @@
         <v>150</v>
       </c>
       <c r="B20" t="s">
-        <v>381</v>
+        <v>356</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>153</v>
@@ -3439,7 +3363,7 @@
         <v>150</v>
       </c>
       <c r="B21" t="s">
-        <v>382</v>
+        <v>357</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>153</v>
@@ -3506,7 +3430,7 @@
         <v>150</v>
       </c>
       <c r="B22" t="s">
-        <v>383</v>
+        <v>358</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>153</v>
@@ -3573,7 +3497,7 @@
         <v>150</v>
       </c>
       <c r="B23" t="s">
-        <v>384</v>
+        <v>359</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>153</v>
@@ -3693,7 +3617,7 @@
         <v>150</v>
       </c>
       <c r="B24" t="s">
-        <v>385</v>
+        <v>360</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>153</v>
@@ -3760,7 +3684,7 @@
         <v>150</v>
       </c>
       <c r="B25" t="s">
-        <v>386</v>
+        <v>361</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>153</v>
@@ -3827,7 +3751,7 @@
         <v>149</v>
       </c>
       <c r="B26" t="s">
-        <v>214</v>
+        <v>191</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>153</v>
@@ -3947,7 +3871,7 @@
         <v>149</v>
       </c>
       <c r="B27" t="s">
-        <v>215</v>
+        <v>192</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>153</v>
@@ -4014,7 +3938,7 @@
         <v>149</v>
       </c>
       <c r="B28" t="s">
-        <v>216</v>
+        <v>193</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>153</v>
@@ -4081,7 +4005,7 @@
         <v>149</v>
       </c>
       <c r="B29" t="s">
-        <v>217</v>
+        <v>194</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>153</v>
@@ -4201,7 +4125,7 @@
         <v>149</v>
       </c>
       <c r="B30" t="s">
-        <v>218</v>
+        <v>195</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>153</v>
@@ -4268,7 +4192,7 @@
         <v>149</v>
       </c>
       <c r="B31" t="s">
-        <v>219</v>
+        <v>196</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>153</v>
@@ -4335,7 +4259,7 @@
         <v>149</v>
       </c>
       <c r="B32" t="s">
-        <v>220</v>
+        <v>197</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>153</v>
@@ -4455,7 +4379,7 @@
         <v>149</v>
       </c>
       <c r="B33" t="s">
-        <v>221</v>
+        <v>198</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>153</v>
@@ -4522,7 +4446,7 @@
         <v>149</v>
       </c>
       <c r="B34" t="s">
-        <v>222</v>
+        <v>199</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>153</v>
@@ -4589,7 +4513,7 @@
         <v>149</v>
       </c>
       <c r="B35" t="s">
-        <v>223</v>
+        <v>200</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>153</v>
@@ -4709,7 +4633,7 @@
         <v>149</v>
       </c>
       <c r="B36" t="s">
-        <v>224</v>
+        <v>201</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>153</v>
@@ -4776,7 +4700,7 @@
         <v>149</v>
       </c>
       <c r="B37" t="s">
-        <v>225</v>
+        <v>202</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>153</v>
@@ -4963,7 +4887,7 @@
         <v>150</v>
       </c>
       <c r="B39" t="s">
-        <v>226</v>
+        <v>203</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>187</v>
@@ -5030,7 +4954,7 @@
         <v>150</v>
       </c>
       <c r="B40" t="s">
-        <v>227</v>
+        <v>204</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>187</v>
@@ -5097,7 +5021,7 @@
         <v>150</v>
       </c>
       <c r="B41" t="s">
-        <v>228</v>
+        <v>205</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>187</v>
@@ -5217,7 +5141,7 @@
         <v>150</v>
       </c>
       <c r="B42" t="s">
-        <v>229</v>
+        <v>206</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>187</v>
@@ -5284,7 +5208,7 @@
         <v>150</v>
       </c>
       <c r="B43" t="s">
-        <v>230</v>
+        <v>207</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>187</v>
@@ -5351,7 +5275,7 @@
         <v>150</v>
       </c>
       <c r="B44" t="s">
-        <v>231</v>
+        <v>208</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>187</v>
@@ -5471,7 +5395,7 @@
         <v>150</v>
       </c>
       <c r="B45" t="s">
-        <v>232</v>
+        <v>209</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>187</v>
@@ -5538,7 +5462,7 @@
         <v>150</v>
       </c>
       <c r="B46" t="s">
-        <v>233</v>
+        <v>210</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>187</v>
@@ -5605,7 +5529,7 @@
         <v>150</v>
       </c>
       <c r="B47" t="s">
-        <v>234</v>
+        <v>211</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>187</v>
@@ -5725,7 +5649,7 @@
         <v>150</v>
       </c>
       <c r="B48" t="s">
-        <v>235</v>
+        <v>212</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>187</v>
@@ -5792,7 +5716,7 @@
         <v>150</v>
       </c>
       <c r="B49" t="s">
-        <v>236</v>
+        <v>213</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>187</v>
@@ -5859,7 +5783,7 @@
         <v>149</v>
       </c>
       <c r="B50" t="s">
-        <v>237</v>
+        <v>214</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>154</v>
@@ -5937,7 +5861,7 @@
         <v>149</v>
       </c>
       <c r="B51" t="s">
-        <v>238</v>
+        <v>215</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>154</v>
@@ -6068,7 +5992,7 @@
         <v>149</v>
       </c>
       <c r="B52" t="s">
-        <v>239</v>
+        <v>216</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>154</v>
@@ -6146,7 +6070,7 @@
         <v>149</v>
       </c>
       <c r="B53" t="s">
-        <v>240</v>
+        <v>217</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>154</v>
@@ -6277,7 +6201,7 @@
         <v>149</v>
       </c>
       <c r="B54" t="s">
-        <v>241</v>
+        <v>218</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>154</v>
@@ -6355,7 +6279,7 @@
         <v>149</v>
       </c>
       <c r="B55" t="s">
-        <v>242</v>
+        <v>219</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>154</v>
@@ -6486,7 +6410,7 @@
         <v>149</v>
       </c>
       <c r="B56" t="s">
-        <v>243</v>
+        <v>220</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>154</v>
@@ -6564,7 +6488,7 @@
         <v>149</v>
       </c>
       <c r="B57" t="s">
-        <v>244</v>
+        <v>221</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>154</v>
@@ -6695,7 +6619,7 @@
         <v>149</v>
       </c>
       <c r="B58" t="s">
-        <v>245</v>
+        <v>222</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>154</v>
@@ -6773,7 +6697,7 @@
         <v>149</v>
       </c>
       <c r="B59" t="s">
-        <v>246</v>
+        <v>223</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>154</v>
@@ -6904,7 +6828,7 @@
         <v>149</v>
       </c>
       <c r="B60" t="s">
-        <v>247</v>
+        <v>224</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>154</v>
@@ -6982,7 +6906,7 @@
         <v>149</v>
       </c>
       <c r="B61" t="s">
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>154</v>
@@ -7116,7 +7040,7 @@
         <v>172</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>358</v>
+        <v>335</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>177</v>
@@ -7244,10 +7168,10 @@
         <v>150</v>
       </c>
       <c r="B63" t="s">
-        <v>249</v>
+        <v>226</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>358</v>
+        <v>335</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>152</v>
@@ -7322,10 +7246,10 @@
         <v>150</v>
       </c>
       <c r="B64" t="s">
-        <v>250</v>
+        <v>227</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>358</v>
+        <v>335</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>152</v>
@@ -7400,10 +7324,10 @@
         <v>150</v>
       </c>
       <c r="B65" t="s">
-        <v>251</v>
+        <v>228</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>358</v>
+        <v>335</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>152</v>
@@ -7531,10 +7455,10 @@
         <v>150</v>
       </c>
       <c r="B66" t="s">
-        <v>252</v>
+        <v>229</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>358</v>
+        <v>335</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>152</v>
@@ -7609,10 +7533,10 @@
         <v>150</v>
       </c>
       <c r="B67" t="s">
-        <v>253</v>
+        <v>230</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>358</v>
+        <v>335</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>152</v>
@@ -7687,10 +7611,10 @@
         <v>150</v>
       </c>
       <c r="B68" t="s">
-        <v>254</v>
+        <v>231</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>358</v>
+        <v>335</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>152</v>
@@ -7818,10 +7742,10 @@
         <v>150</v>
       </c>
       <c r="B69" t="s">
-        <v>255</v>
+        <v>232</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>358</v>
+        <v>335</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>152</v>
@@ -7896,10 +7820,10 @@
         <v>150</v>
       </c>
       <c r="B70" t="s">
-        <v>256</v>
+        <v>233</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>358</v>
+        <v>335</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>152</v>
@@ -7974,10 +7898,10 @@
         <v>150</v>
       </c>
       <c r="B71" t="s">
-        <v>257</v>
+        <v>234</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>358</v>
+        <v>335</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>152</v>
@@ -8105,10 +8029,10 @@
         <v>150</v>
       </c>
       <c r="B72" t="s">
-        <v>258</v>
+        <v>235</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>358</v>
+        <v>335</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>152</v>
@@ -8183,10 +8107,10 @@
         <v>150</v>
       </c>
       <c r="B73" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>358</v>
+        <v>335</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>152</v>
@@ -8261,7 +8185,7 @@
         <v>149</v>
       </c>
       <c r="B74" t="s">
-        <v>260</v>
+        <v>237</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>155</v>
@@ -8339,7 +8263,7 @@
         <v>149</v>
       </c>
       <c r="B75" t="s">
-        <v>261</v>
+        <v>238</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>155</v>
@@ -8470,7 +8394,7 @@
         <v>149</v>
       </c>
       <c r="B76" t="s">
-        <v>262</v>
+        <v>239</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>155</v>
@@ -8548,7 +8472,7 @@
         <v>149</v>
       </c>
       <c r="B77" t="s">
-        <v>263</v>
+        <v>240</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>155</v>
@@ -8679,7 +8603,7 @@
         <v>149</v>
       </c>
       <c r="B78" t="s">
-        <v>264</v>
+        <v>241</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>155</v>
@@ -8757,7 +8681,7 @@
         <v>149</v>
       </c>
       <c r="B79" t="s">
-        <v>265</v>
+        <v>242</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>155</v>
@@ -8888,7 +8812,7 @@
         <v>149</v>
       </c>
       <c r="B80" t="s">
-        <v>266</v>
+        <v>243</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>155</v>
@@ -8966,7 +8890,7 @@
         <v>149</v>
       </c>
       <c r="B81" t="s">
-        <v>267</v>
+        <v>244</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>155</v>
@@ -9097,7 +9021,7 @@
         <v>149</v>
       </c>
       <c r="B82" t="s">
-        <v>268</v>
+        <v>245</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>155</v>
@@ -9175,7 +9099,7 @@
         <v>149</v>
       </c>
       <c r="B83" t="s">
-        <v>269</v>
+        <v>246</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>155</v>
@@ -9306,7 +9230,7 @@
         <v>149</v>
       </c>
       <c r="B84" t="s">
-        <v>270</v>
+        <v>247</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>155</v>
@@ -9384,7 +9308,7 @@
         <v>149</v>
       </c>
       <c r="B85" t="s">
-        <v>271</v>
+        <v>248</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>155</v>
@@ -9518,7 +9442,7 @@
         <v>173</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>359</v>
+        <v>336</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>177</v>
@@ -9646,10 +9570,10 @@
         <v>150</v>
       </c>
       <c r="B87" t="s">
-        <v>272</v>
+        <v>249</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>359</v>
+        <v>336</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>152</v>
@@ -9724,10 +9648,10 @@
         <v>150</v>
       </c>
       <c r="B88" t="s">
-        <v>273</v>
+        <v>250</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>359</v>
+        <v>336</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>152</v>
@@ -9802,10 +9726,10 @@
         <v>150</v>
       </c>
       <c r="B89" t="s">
-        <v>274</v>
+        <v>251</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>359</v>
+        <v>336</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>152</v>
@@ -9933,10 +9857,10 @@
         <v>150</v>
       </c>
       <c r="B90" t="s">
-        <v>275</v>
+        <v>252</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>359</v>
+        <v>336</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>152</v>
@@ -10011,10 +9935,10 @@
         <v>150</v>
       </c>
       <c r="B91" t="s">
-        <v>276</v>
+        <v>253</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>359</v>
+        <v>336</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>152</v>
@@ -10089,10 +10013,10 @@
         <v>150</v>
       </c>
       <c r="B92" t="s">
-        <v>277</v>
+        <v>254</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>359</v>
+        <v>336</v>
       </c>
       <c r="D92" s="1" t="s">
         <v>152</v>
@@ -10220,10 +10144,10 @@
         <v>150</v>
       </c>
       <c r="B93" t="s">
-        <v>278</v>
+        <v>255</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>359</v>
+        <v>336</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>152</v>
@@ -10298,10 +10222,10 @@
         <v>150</v>
       </c>
       <c r="B94" t="s">
-        <v>279</v>
+        <v>256</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>359</v>
+        <v>336</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>152</v>
@@ -10376,10 +10300,10 @@
         <v>150</v>
       </c>
       <c r="B95" t="s">
-        <v>280</v>
+        <v>257</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>359</v>
+        <v>336</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>152</v>
@@ -10507,10 +10431,10 @@
         <v>150</v>
       </c>
       <c r="B96" t="s">
-        <v>281</v>
+        <v>258</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>359</v>
+        <v>336</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>152</v>
@@ -10585,10 +10509,10 @@
         <v>150</v>
       </c>
       <c r="B97" t="s">
-        <v>282</v>
+        <v>259</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>359</v>
+        <v>336</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>152</v>
@@ -10663,7 +10587,7 @@
         <v>149</v>
       </c>
       <c r="B98" t="s">
-        <v>283</v>
+        <v>260</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>156</v>
@@ -10721,7 +10645,7 @@
         <v>149</v>
       </c>
       <c r="B99" t="s">
-        <v>284</v>
+        <v>261</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>156</v>
@@ -10779,7 +10703,7 @@
         <v>149</v>
       </c>
       <c r="B100" t="s">
-        <v>285</v>
+        <v>262</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>156</v>
@@ -10837,10 +10761,10 @@
         <v>150</v>
       </c>
       <c r="B101" t="s">
-        <v>286</v>
+        <v>263</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>360</v>
+        <v>337</v>
       </c>
       <c r="D101" s="1" t="s">
         <v>152</v>
@@ -10895,10 +10819,10 @@
         <v>150</v>
       </c>
       <c r="B102" t="s">
-        <v>287</v>
+        <v>264</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>360</v>
+        <v>337</v>
       </c>
       <c r="D102" s="1" t="s">
         <v>152</v>
@@ -10953,10 +10877,10 @@
         <v>150</v>
       </c>
       <c r="B103" t="s">
-        <v>288</v>
+        <v>265</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>360</v>
+        <v>337</v>
       </c>
       <c r="D103" s="1" t="s">
         <v>152</v>
@@ -11011,7 +10935,7 @@
         <v>149</v>
       </c>
       <c r="B104" t="s">
-        <v>289</v>
+        <v>266</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>157</v>
@@ -11097,7 +11021,7 @@
         <v>149</v>
       </c>
       <c r="B106" t="s">
-        <v>290</v>
+        <v>267</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>159</v>
@@ -11143,7 +11067,7 @@
         <v>149</v>
       </c>
       <c r="B107" t="s">
-        <v>291</v>
+        <v>268</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>160</v>
@@ -11189,7 +11113,7 @@
         <v>149</v>
       </c>
       <c r="B108" t="s">
-        <v>292</v>
+        <v>269</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>157</v>
@@ -11275,7 +11199,7 @@
         <v>149</v>
       </c>
       <c r="B110" t="s">
-        <v>293</v>
+        <v>270</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>159</v>
@@ -11321,7 +11245,7 @@
         <v>149</v>
       </c>
       <c r="B111" t="s">
-        <v>294</v>
+        <v>271</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>160</v>
@@ -11367,7 +11291,7 @@
         <v>149</v>
       </c>
       <c r="B112" t="s">
-        <v>295</v>
+        <v>272</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>157</v>
@@ -11453,7 +11377,7 @@
         <v>149</v>
       </c>
       <c r="B114" t="s">
-        <v>296</v>
+        <v>273</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>159</v>
@@ -11499,7 +11423,7 @@
         <v>149</v>
       </c>
       <c r="B115" t="s">
-        <v>297</v>
+        <v>274</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>160</v>
@@ -11545,7 +11469,7 @@
         <v>150</v>
       </c>
       <c r="B116" t="s">
-        <v>298</v>
+        <v>275</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>161</v>
@@ -11665,7 +11589,7 @@
         <v>150</v>
       </c>
       <c r="B117" t="s">
-        <v>299</v>
+        <v>276</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>161</v>
@@ -11785,7 +11709,7 @@
         <v>150</v>
       </c>
       <c r="B118" t="s">
-        <v>300</v>
+        <v>277</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>161</v>
@@ -11905,7 +11829,7 @@
         <v>150</v>
       </c>
       <c r="B119" t="s">
-        <v>301</v>
+        <v>278</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>161</v>
@@ -12025,7 +11949,7 @@
         <v>150</v>
       </c>
       <c r="B120" t="s">
-        <v>302</v>
+        <v>279</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>161</v>
@@ -12145,7 +12069,7 @@
         <v>150</v>
       </c>
       <c r="B121" t="s">
-        <v>303</v>
+        <v>280</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>161</v>
@@ -12265,7 +12189,7 @@
         <v>150</v>
       </c>
       <c r="B122" t="s">
-        <v>304</v>
+        <v>281</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>161</v>
@@ -12385,7 +12309,7 @@
         <v>150</v>
       </c>
       <c r="B123" t="s">
-        <v>305</v>
+        <v>282</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>161</v>
@@ -12505,7 +12429,7 @@
         <v>150</v>
       </c>
       <c r="B124" t="s">
-        <v>306</v>
+        <v>283</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>161</v>
@@ -12625,7 +12549,7 @@
         <v>150</v>
       </c>
       <c r="B125" t="s">
-        <v>307</v>
+        <v>284</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>161</v>
@@ -12745,7 +12669,7 @@
         <v>150</v>
       </c>
       <c r="B126" t="s">
-        <v>308</v>
+        <v>285</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>161</v>
@@ -12865,7 +12789,7 @@
         <v>150</v>
       </c>
       <c r="B127" t="s">
-        <v>309</v>
+        <v>286</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>161</v>
@@ -12985,7 +12909,7 @@
         <v>149</v>
       </c>
       <c r="B128" t="s">
-        <v>310</v>
+        <v>287</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>170</v>
@@ -13105,7 +13029,7 @@
         <v>149</v>
       </c>
       <c r="B129" t="s">
-        <v>311</v>
+        <v>288</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>170</v>
@@ -13225,7 +13149,7 @@
         <v>149</v>
       </c>
       <c r="B130" t="s">
-        <v>312</v>
+        <v>289</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>170</v>
@@ -13345,7 +13269,7 @@
         <v>149</v>
       </c>
       <c r="B131" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>170</v>
@@ -13465,7 +13389,7 @@
         <v>149</v>
       </c>
       <c r="B132" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>170</v>
@@ -13585,7 +13509,7 @@
         <v>149</v>
       </c>
       <c r="B133" t="s">
-        <v>315</v>
+        <v>292</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>170</v>
@@ -13705,7 +13629,7 @@
         <v>149</v>
       </c>
       <c r="B134" t="s">
-        <v>316</v>
+        <v>293</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>170</v>
@@ -13825,7 +13749,7 @@
         <v>149</v>
       </c>
       <c r="B135" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>170</v>
@@ -13945,7 +13869,7 @@
         <v>149</v>
       </c>
       <c r="B136" t="s">
-        <v>318</v>
+        <v>295</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>170</v>
@@ -14065,7 +13989,7 @@
         <v>149</v>
       </c>
       <c r="B137" t="s">
-        <v>319</v>
+        <v>296</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>170</v>
@@ -14185,7 +14109,7 @@
         <v>149</v>
       </c>
       <c r="B138" t="s">
-        <v>320</v>
+        <v>297</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>170</v>
@@ -14305,7 +14229,7 @@
         <v>149</v>
       </c>
       <c r="B139" t="s">
-        <v>321</v>
+        <v>298</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>170</v>
@@ -14425,7 +14349,7 @@
         <v>149</v>
       </c>
       <c r="B140" t="s">
-        <v>322</v>
+        <v>299</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>181</v>
@@ -14545,7 +14469,7 @@
         <v>149</v>
       </c>
       <c r="B141" t="s">
-        <v>323</v>
+        <v>300</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>181</v>
@@ -14665,7 +14589,7 @@
         <v>149</v>
       </c>
       <c r="B142" t="s">
-        <v>324</v>
+        <v>301</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>181</v>
@@ -14785,7 +14709,7 @@
         <v>149</v>
       </c>
       <c r="B143" t="s">
-        <v>325</v>
+        <v>302</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>181</v>
@@ -14905,7 +14829,7 @@
         <v>149</v>
       </c>
       <c r="B144" t="s">
-        <v>326</v>
+        <v>303</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>181</v>
@@ -15025,7 +14949,7 @@
         <v>149</v>
       </c>
       <c r="B145" t="s">
-        <v>327</v>
+        <v>304</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>181</v>
@@ -15145,7 +15069,7 @@
         <v>149</v>
       </c>
       <c r="B146" t="s">
-        <v>328</v>
+        <v>305</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>181</v>
@@ -15265,7 +15189,7 @@
         <v>149</v>
       </c>
       <c r="B147" t="s">
-        <v>329</v>
+        <v>306</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>181</v>
@@ -15385,7 +15309,7 @@
         <v>149</v>
       </c>
       <c r="B148" t="s">
-        <v>330</v>
+        <v>307</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>181</v>
@@ -15505,7 +15429,7 @@
         <v>149</v>
       </c>
       <c r="B149" t="s">
-        <v>331</v>
+        <v>308</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>181</v>
@@ -15625,7 +15549,7 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>332</v>
+        <v>309</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>181</v>
@@ -15745,7 +15669,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>333</v>
+        <v>310</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>181</v>
@@ -15865,7 +15789,7 @@
         <v>149</v>
       </c>
       <c r="B152" t="s">
-        <v>334</v>
+        <v>311</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>185</v>
@@ -15985,7 +15909,7 @@
         <v>149</v>
       </c>
       <c r="B153" t="s">
-        <v>335</v>
+        <v>312</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>185</v>
@@ -16105,7 +16029,7 @@
         <v>149</v>
       </c>
       <c r="B154" t="s">
-        <v>336</v>
+        <v>313</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>185</v>
@@ -16225,7 +16149,7 @@
         <v>149</v>
       </c>
       <c r="B155" t="s">
-        <v>337</v>
+        <v>314</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>185</v>
@@ -16345,7 +16269,7 @@
         <v>149</v>
       </c>
       <c r="B156" t="s">
-        <v>338</v>
+        <v>315</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>185</v>
@@ -16465,7 +16389,7 @@
         <v>149</v>
       </c>
       <c r="B157" t="s">
-        <v>339</v>
+        <v>316</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>185</v>
@@ -16585,7 +16509,7 @@
         <v>149</v>
       </c>
       <c r="B158" t="s">
-        <v>340</v>
+        <v>317</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>185</v>
@@ -16705,7 +16629,7 @@
         <v>149</v>
       </c>
       <c r="B159" t="s">
-        <v>341</v>
+        <v>318</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>185</v>
@@ -16825,7 +16749,7 @@
         <v>149</v>
       </c>
       <c r="B160" t="s">
-        <v>342</v>
+        <v>319</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>185</v>
@@ -16945,7 +16869,7 @@
         <v>149</v>
       </c>
       <c r="B161" t="s">
-        <v>343</v>
+        <v>320</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>185</v>
@@ -17065,7 +16989,7 @@
         <v>149</v>
       </c>
       <c r="B162" t="s">
-        <v>344</v>
+        <v>321</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>185</v>
@@ -17185,7 +17109,7 @@
         <v>149</v>
       </c>
       <c r="B163" t="s">
-        <v>345</v>
+        <v>322</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>185</v>
@@ -17305,7 +17229,7 @@
         <v>149</v>
       </c>
       <c r="B164" t="s">
-        <v>346</v>
+        <v>323</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>187</v>
@@ -17425,7 +17349,7 @@
         <v>149</v>
       </c>
       <c r="B165" t="s">
-        <v>347</v>
+        <v>324</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>187</v>
@@ -17545,7 +17469,7 @@
         <v>149</v>
       </c>
       <c r="B166" t="s">
-        <v>348</v>
+        <v>325</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>187</v>
@@ -17665,7 +17589,7 @@
         <v>150</v>
       </c>
       <c r="B167" t="s">
-        <v>349</v>
+        <v>326</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>187</v>
@@ -17785,7 +17709,7 @@
         <v>150</v>
       </c>
       <c r="B168" t="s">
-        <v>350</v>
+        <v>327</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>187</v>
@@ -17905,7 +17829,7 @@
         <v>150</v>
       </c>
       <c r="B169" t="s">
-        <v>351</v>
+        <v>328</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>187</v>
@@ -18025,7 +17949,7 @@
         <v>149</v>
       </c>
       <c r="B170" t="s">
-        <v>352</v>
+        <v>329</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>187</v>
@@ -18145,7 +18069,7 @@
         <v>149</v>
       </c>
       <c r="B171" t="s">
-        <v>353</v>
+        <v>330</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>187</v>
@@ -18265,7 +18189,7 @@
         <v>149</v>
       </c>
       <c r="B172" t="s">
-        <v>354</v>
+        <v>331</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>187</v>
@@ -18385,7 +18309,7 @@
         <v>149</v>
       </c>
       <c r="B173" t="s">
-        <v>355</v>
+        <v>332</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>187</v>
@@ -18505,7 +18429,7 @@
         <v>149</v>
       </c>
       <c r="B174" t="s">
-        <v>356</v>
+        <v>333</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>187</v>
@@ -18625,7 +18549,7 @@
         <v>149</v>
       </c>
       <c r="B175" t="s">
-        <v>357</v>
+        <v>334</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>187</v>
@@ -18743,8 +18667,8 @@
   </sheetData>
   <autoFilter ref="G1:G175" xr:uid="{01D907F6-7637-41F5-9F0A-BDDAA86240AA}"/>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup horizontalDpi="4294967293" orientation="portrait" r:id="rId1" verticalDpi="0"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>
@@ -18752,68 +18676,68 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E373AFE3-95E6-4012-963C-FB304E9ADB66}">
-  <dimension ref="A1:AX115"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E373AFE3-95E6-4012-963C-FB304E9ADB66}">
+  <dimension ref="A1:AW115"/>
   <sheetFormatPr defaultColWidth="26.73046875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" style="1" width="26.73046875" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="32.0" collapsed="true"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="9.19921875" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="4.73046875" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="6.46484375" collapsed="true"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="10.0" collapsed="true"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="9.46484375" collapsed="true"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="11.73046875" collapsed="true"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" style="1" width="8.796875" collapsed="true"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="6.73046875" collapsed="true"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="13.73046875" collapsed="true"/>
-    <col min="13" max="13" customWidth="true" style="1" width="19.19921875" collapsed="true"/>
-    <col min="14" max="14" customWidth="true" style="1" width="22.265625" collapsed="true"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="8.0" collapsed="true"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" style="1" width="9.265625" collapsed="true"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="5.53125" collapsed="true"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="6.0" collapsed="true"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="9.796875" collapsed="true"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="8.19921875" collapsed="true"/>
-    <col min="21" max="21" customWidth="true" style="1" width="24.0" collapsed="true"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="4.73046875" collapsed="true"/>
-    <col min="23" max="23" customWidth="true" style="1" width="8.796875" collapsed="true"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" style="1" width="8.73046875" collapsed="true"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" style="1" width="9.265625" collapsed="true"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" style="1" width="115.46484375" collapsed="true"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="75.53125" collapsed="true"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="40.53125" collapsed="true"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="14.46484375" collapsed="true"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="23.796875" collapsed="true"/>
-    <col min="31" max="31" bestFit="true" customWidth="true" style="1" width="13.53125" collapsed="true"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="11.19921875" collapsed="true"/>
-    <col min="33" max="33" bestFit="true" customWidth="true" style="1" width="18.0" collapsed="true"/>
-    <col min="34" max="34" bestFit="true" customWidth="true" style="1" width="7.0" collapsed="true"/>
-    <col min="35" max="35" bestFit="true" customWidth="true" style="1" width="14.73046875" collapsed="true"/>
-    <col min="36" max="44" bestFit="true" customWidth="true" style="1" width="10.46484375" collapsed="true"/>
-    <col min="45" max="45" bestFit="true" customWidth="true" style="1" width="11.46484375" collapsed="true"/>
-    <col min="46" max="47" bestFit="true" customWidth="true" style="1" width="13.73046875" collapsed="true"/>
-    <col min="48" max="48" customWidth="true" style="1" width="12.53125" collapsed="true"/>
-    <col min="49" max="49" customWidth="true" style="1" width="15.0" collapsed="true"/>
-    <col min="50" max="50" bestFit="true" customWidth="true" style="1" width="14.46484375" collapsed="true"/>
-    <col min="51" max="51" bestFit="true" customWidth="true" style="1" width="9.19921875" collapsed="true"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" style="1" width="12.0" collapsed="true"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" style="1" width="11.53125" collapsed="true"/>
-    <col min="54" max="54" bestFit="true" customWidth="true" style="1" width="15.265625" collapsed="true"/>
-    <col min="55" max="55" bestFit="true" customWidth="true" style="1" width="14.73046875" collapsed="true"/>
-    <col min="56" max="56" bestFit="true" customWidth="true" style="1" width="15.73046875" collapsed="true"/>
-    <col min="57" max="57" bestFit="true" customWidth="true" style="1" width="11.796875" collapsed="true"/>
-    <col min="58" max="58" bestFit="true" customWidth="true" style="1" width="18.265625" collapsed="true"/>
-    <col min="59" max="59" bestFit="true" customWidth="true" style="1" width="14.796875" collapsed="true"/>
-    <col min="60" max="61" bestFit="true" customWidth="true" style="1" width="15.796875" collapsed="true"/>
-    <col min="62" max="62" bestFit="true" customWidth="true" style="1" width="16.46484375" collapsed="true"/>
-    <col min="63" max="63" bestFit="true" customWidth="true" style="1" width="10.0" collapsed="true"/>
-    <col min="64" max="64" bestFit="true" customWidth="true" style="1" width="10.73046875" collapsed="true"/>
-    <col min="65" max="16384" style="1" width="26.73046875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="26.73046875" style="1" collapsed="1"/>
+    <col min="3" max="3" width="32" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="9.19921875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="4.73046875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="6.46484375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="10" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="9.46484375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="11.73046875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="8.796875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="6.73046875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="12" max="12" width="13.73046875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="13" max="13" width="19.19921875" style="1" customWidth="1" collapsed="1"/>
+    <col min="14" max="14" width="22.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="15" max="15" width="8" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="16" max="16" width="9.265625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="17" max="17" width="5.53125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="18" max="18" width="6" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="19" max="19" width="9.796875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="20" max="20" width="8.19921875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="21" max="21" width="24" style="1" customWidth="1" collapsed="1"/>
+    <col min="22" max="22" width="4.73046875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="23" max="23" width="8.796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="24" max="24" width="8.73046875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="25" max="25" width="9.265625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="26" max="26" width="115.46484375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="27" max="27" width="75.53125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="28" max="28" width="40.53125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="29" max="29" width="14.46484375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="30" max="30" width="23.796875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="31" max="31" width="13.53125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="32" max="32" width="11.19921875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="33" max="33" width="18" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="34" max="34" width="7" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="35" max="35" width="14.73046875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="36" max="44" width="10.46484375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="45" max="45" width="11.46484375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="46" max="47" width="13.73046875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="48" max="48" width="12.53125" style="1" customWidth="1" collapsed="1"/>
+    <col min="49" max="49" width="15" style="1" customWidth="1" collapsed="1"/>
+    <col min="50" max="50" width="14.46484375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="51" max="51" width="9.19921875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="52" max="52" width="12" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="53" max="53" width="11.53125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="54" max="54" width="15.265625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="55" max="55" width="14.73046875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="56" max="56" width="15.73046875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="57" max="57" width="11.796875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="58" max="58" width="18.265625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="59" max="59" width="14.796875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="60" max="61" width="15.796875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="62" max="62" width="16.46484375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="63" max="63" width="10" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="64" max="64" width="10.73046875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="65" max="16384" width="26.73046875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row ht="28.5" r="1" spans="1:49" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:49" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>145</v>
       </c>
@@ -28227,7 +28151,7 @@
       <c r="AW115" s="2"/>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>
@@ -28235,14 +28159,14 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97E51003-E6AF-4A46-8DE2-C02177084CDE}">
-  <dimension ref="A1:BT1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97E51003-E6AF-4A46-8DE2-C02177084CDE}">
+  <dimension ref="A1:BS1"/>
   <sheetFormatPr defaultColWidth="20.46484375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="16384" style="1" width="20.46484375" collapsed="true"/>
+    <col min="1" max="16384" width="20.46484375" style="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row ht="28.5" r="1" spans="1:71" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:71" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -28458,8 +28382,8 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup horizontalDpi="4294967293" orientation="portrait" r:id="rId1" verticalDpi="0"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>
